--- a/public/data/Edition_Slab_Matrix.xlsx
+++ b/public/data/Edition_Slab_Matrix.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Milestones CRM\Till May-26\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Milestones CRM\Till Jun-26\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D48C9C25-C95F-4E63-A3CA-B226FC224CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C9F8AB-A215-4608-ADC4-7ABF938BAE27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{717DAC09-61D3-4262-BE82-6B1D9CCC4A78}"/>
   </bookViews>
   <sheets>
     <sheet name="% Progress" sheetId="3" r:id="rId1"/>
-    <sheet name="01.06.26 Revised" sheetId="1" r:id="rId2"/>
+    <sheet name="29.06.26 Revised" sheetId="1" r:id="rId2"/>
     <sheet name="Revised CRM milestones" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'01.06.26 Revised'!$A$1:$AD$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'29.06.26 Revised'!$A$1:$AD$58</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -664,7 +664,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="52">
+  <borders count="54">
     <border>
       <left/>
       <right/>
@@ -1335,12 +1335,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB1BBCC"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB1BBCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB1BBCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB1BBCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="13" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="165">
+  <cellXfs count="164">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="1" fillId="10" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1470,18 +1492,6 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="7" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="10" fillId="6" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1510,12 +1520,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="10" fillId="6" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1723,6 +1727,72 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="11" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="6" fillId="11" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="17" fontId="1" fillId="11" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1770,57 +1840,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="10" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="10" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="10" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="10" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="11" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="11" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="6" fillId="11" borderId="41" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="6" fillId="11" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="11" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="17" fontId="1" fillId="11" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2108,680 +2127,685 @@
   <cols>
     <col min="1" max="1" width="5.54296875" customWidth="1"/>
     <col min="2" max="2" width="39.453125" customWidth="1"/>
-    <col min="3" max="5" width="19.1796875" style="116" customWidth="1"/>
+    <col min="3" max="5" width="19.1796875" style="110" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="2:6" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="132" t="s">
+      <c r="B2" s="148" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="134" t="s">
+      <c r="C2" s="150" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="135"/>
-      <c r="E2" s="136"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="152"/>
     </row>
     <row r="3" spans="2:6" ht="93" x14ac:dyDescent="0.35">
-      <c r="B3" s="133"/>
-      <c r="C3" s="117" t="s">
+      <c r="B3" s="149"/>
+      <c r="C3" s="111" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="117" t="s">
+      <c r="D3" s="111" t="s">
         <v>85</v>
       </c>
-      <c r="E3" s="118" t="s">
+      <c r="E3" s="112" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="119" t="s">
+      <c r="B4" s="113" t="s">
         <v>87</v>
       </c>
-      <c r="C4" s="137" t="s">
+      <c r="C4" s="153" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="137"/>
-      <c r="E4" s="121">
+      <c r="D4" s="153"/>
+      <c r="E4" s="115">
         <v>0.99</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="119" t="s">
+      <c r="B5" s="113" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="137"/>
-      <c r="D5" s="137"/>
-      <c r="E5" s="121">
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="115">
         <v>0.7</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B6" s="119" t="s">
+      <c r="B6" s="113" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="137" t="s">
+      <c r="C6" s="153" t="s">
         <v>88</v>
       </c>
-      <c r="D6" s="137"/>
-      <c r="E6" s="121">
+      <c r="D6" s="153"/>
+      <c r="E6" s="115">
         <v>0.7</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B7" s="119" t="s">
+      <c r="B7" s="113" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="120">
+      <c r="C7" s="114">
         <v>6</v>
       </c>
-      <c r="D7" s="120">
+      <c r="D7" s="114">
         <v>6</v>
       </c>
-      <c r="E7" s="121">
+      <c r="E7" s="115">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B8" s="119" t="s">
+      <c r="B8" s="113" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="137" t="s">
+      <c r="C8" s="153" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="137"/>
-      <c r="E8" s="121">
+      <c r="D8" s="153"/>
+      <c r="E8" s="115">
         <v>0.3</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B9" s="119" t="s">
+      <c r="B9" s="113" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="120">
+      <c r="C9" s="114">
         <v>6</v>
       </c>
-      <c r="D9" s="120">
+      <c r="D9" s="114">
         <v>6</v>
       </c>
-      <c r="E9" s="121">
+      <c r="E9" s="115">
         <v>1</v>
       </c>
-      <c r="F9" s="122"/>
+      <c r="F9" s="116"/>
     </row>
     <row r="10" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="119" t="s">
+      <c r="B10" s="113" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="120">
+      <c r="C10" s="114">
         <v>6</v>
       </c>
-      <c r="D10" s="120">
+      <c r="D10" s="114">
         <v>6</v>
       </c>
-      <c r="E10" s="121">
+      <c r="E10" s="115">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="119" t="s">
+      <c r="B11" s="113" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="120">
+      <c r="C11" s="114">
         <v>6</v>
       </c>
-      <c r="D11" s="120">
+      <c r="D11" s="114">
         <v>6</v>
       </c>
-      <c r="E11" s="121">
+      <c r="E11" s="115">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="119" t="s">
+      <c r="B12" s="113" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="120">
+      <c r="C12" s="114">
         <v>6</v>
       </c>
-      <c r="D12" s="120">
+      <c r="D12" s="114">
         <v>6</v>
       </c>
-      <c r="E12" s="121">
+      <c r="E12" s="115">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="119" t="s">
+      <c r="B13" s="113" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="120">
+      <c r="C13" s="114">
         <v>6</v>
       </c>
-      <c r="D13" s="120">
+      <c r="D13" s="114">
         <v>6</v>
       </c>
-      <c r="E13" s="121">
+      <c r="E13" s="115">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="119" t="s">
+      <c r="B14" s="113" t="s">
         <v>98</v>
       </c>
-      <c r="C14" s="120">
+      <c r="C14" s="114">
         <v>6</v>
       </c>
-      <c r="D14" s="120">
+      <c r="D14" s="114">
         <v>6</v>
       </c>
-      <c r="E14" s="121">
+      <c r="E14" s="115">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="119" t="s">
+      <c r="B15" s="113" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="120">
+      <c r="C15" s="114">
         <v>6</v>
       </c>
-      <c r="D15" s="120">
+      <c r="D15" s="114">
         <v>6</v>
       </c>
-      <c r="E15" s="121">
+      <c r="E15" s="115">
         <f>D15/C15</f>
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="119" t="s">
+      <c r="B16" s="113" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="120">
+      <c r="C16" s="114">
         <v>6</v>
       </c>
-      <c r="D16" s="120">
+      <c r="D16" s="114">
         <v>6</v>
       </c>
-      <c r="E16" s="121">
-        <f t="shared" ref="E16:E28" si="0">D16/C16</f>
+      <c r="E16" s="115">
+        <f t="shared" ref="E16:E29" si="0">D16/C16</f>
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="119" t="s">
+      <c r="B17" s="113" t="s">
         <v>101</v>
       </c>
-      <c r="C17" s="120">
+      <c r="C17" s="114">
         <v>6</v>
       </c>
-      <c r="D17" s="120">
+      <c r="D17" s="114">
         <v>6</v>
       </c>
-      <c r="E17" s="121">
+      <c r="E17" s="115">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="119" t="s">
+      <c r="B18" s="113" t="s">
         <v>102</v>
       </c>
-      <c r="C18" s="120">
+      <c r="C18" s="114">
         <v>6</v>
       </c>
-      <c r="D18" s="120">
+      <c r="D18" s="114">
         <v>6</v>
       </c>
-      <c r="E18" s="121">
+      <c r="E18" s="115">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="113" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="120">
+      <c r="C19" s="114">
         <v>6</v>
       </c>
-      <c r="D19" s="120">
+      <c r="D19" s="114">
         <v>6</v>
       </c>
-      <c r="E19" s="121">
+      <c r="E19" s="115">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="119" t="s">
+      <c r="B20" s="113" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="120">
+      <c r="C20" s="114">
         <v>6</v>
       </c>
-      <c r="D20" s="120">
+      <c r="D20" s="114">
         <v>6</v>
       </c>
-      <c r="E20" s="121">
+      <c r="E20" s="115">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="113" t="s">
         <v>105</v>
       </c>
-      <c r="C21" s="120">
+      <c r="C21" s="114">
         <v>6</v>
       </c>
-      <c r="D21" s="120">
+      <c r="D21" s="114">
         <v>6</v>
       </c>
-      <c r="E21" s="121">
+      <c r="E21" s="115">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="119" t="s">
+      <c r="B22" s="113" t="s">
         <v>106</v>
       </c>
-      <c r="C22" s="120">
+      <c r="C22" s="114">
         <v>6</v>
       </c>
-      <c r="D22" s="120">
+      <c r="D22" s="114">
         <v>6</v>
       </c>
-      <c r="E22" s="121">
+      <c r="E22" s="115">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="119" t="s">
+      <c r="B23" s="113" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="120">
+      <c r="C23" s="114">
         <v>6</v>
       </c>
-      <c r="D23" s="120">
+      <c r="D23" s="114">
+        <v>6</v>
+      </c>
+      <c r="E23" s="115">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B24" s="113" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="114">
+        <v>6</v>
+      </c>
+      <c r="D24" s="114">
         <v>5</v>
       </c>
-      <c r="E23" s="121">
+      <c r="E24" s="115">
         <f t="shared" si="0"/>
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="24" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="119" t="s">
-        <v>108</v>
-      </c>
-      <c r="C24" s="120">
+    <row r="25" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B25" s="113" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="114">
         <v>6</v>
       </c>
-      <c r="D24" s="120">
+      <c r="D25" s="114">
         <v>4</v>
       </c>
-      <c r="E24" s="121">
+      <c r="E25" s="115">
         <f t="shared" si="0"/>
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="119" t="s">
-        <v>109</v>
-      </c>
-      <c r="C25" s="120">
+    <row r="26" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B26" s="113" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="114">
         <v>6</v>
       </c>
-      <c r="D25" s="120">
+      <c r="D26" s="114">
         <v>3</v>
       </c>
-      <c r="E25" s="121">
+      <c r="E26" s="115">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
     </row>
-    <row r="26" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B26" s="119" t="s">
-        <v>110</v>
-      </c>
-      <c r="C26" s="120">
+    <row r="27" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="113" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" s="114">
         <v>6</v>
       </c>
-      <c r="D26" s="120">
+      <c r="D27" s="125">
         <v>2</v>
       </c>
-      <c r="E26" s="121">
+      <c r="E27" s="115">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B27" s="119" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="120">
+    <row r="28" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B28" s="113" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="114">
         <v>6</v>
       </c>
-      <c r="D27" s="131">
+      <c r="D28" s="125">
         <v>2</v>
       </c>
-      <c r="E27" s="121">
+      <c r="E28" s="115">
         <f t="shared" si="0"/>
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="28" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B28" s="119" t="s">
-        <v>112</v>
-      </c>
-      <c r="C28" s="120">
+    <row r="29" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="113" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="114">
         <v>6</v>
       </c>
-      <c r="D28" s="131">
+      <c r="D29" s="125">
         <v>1</v>
       </c>
-      <c r="E28" s="121">
+      <c r="E29" s="115">
         <f t="shared" si="0"/>
         <v>0.16666666666666666</v>
       </c>
     </row>
-    <row r="29" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="119" t="s">
-        <v>113</v>
-      </c>
-      <c r="C29" s="120">
+    <row r="30" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B30" s="113" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" s="114">
         <v>6</v>
       </c>
-      <c r="D29" s="123"/>
-      <c r="E29" s="124"/>
-    </row>
-    <row r="30" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="119" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" s="120">
+      <c r="D30" s="117"/>
+      <c r="E30" s="118"/>
+    </row>
+    <row r="31" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B31" s="113" t="s">
+        <v>115</v>
+      </c>
+      <c r="C31" s="114">
         <v>6</v>
       </c>
-      <c r="D30" s="123"/>
-      <c r="E30" s="124"/>
-    </row>
-    <row r="31" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B31" s="119" t="s">
-        <v>115</v>
-      </c>
-      <c r="C31" s="120">
+      <c r="D31" s="117"/>
+      <c r="E31" s="118"/>
+    </row>
+    <row r="32" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B32" s="113" t="s">
+        <v>116</v>
+      </c>
+      <c r="C32" s="114">
         <v>6</v>
       </c>
-      <c r="D31" s="123"/>
-      <c r="E31" s="124"/>
-    </row>
-    <row r="32" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B32" s="119" t="s">
-        <v>116</v>
-      </c>
-      <c r="C32" s="120">
+      <c r="D32" s="117"/>
+      <c r="E32" s="118"/>
+    </row>
+    <row r="33" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B33" s="113" t="s">
+        <v>117</v>
+      </c>
+      <c r="C33" s="114">
         <v>6</v>
       </c>
-      <c r="D32" s="123"/>
-      <c r="E32" s="124"/>
-    </row>
-    <row r="33" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B33" s="119" t="s">
-        <v>117</v>
-      </c>
-      <c r="C33" s="120">
+      <c r="D33" s="117"/>
+      <c r="E33" s="118"/>
+    </row>
+    <row r="34" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="113" t="s">
+        <v>118</v>
+      </c>
+      <c r="C34" s="114">
         <v>6</v>
       </c>
-      <c r="D33" s="123"/>
-      <c r="E33" s="124"/>
-    </row>
-    <row r="34" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B34" s="119" t="s">
-        <v>118</v>
-      </c>
-      <c r="C34" s="120">
+      <c r="D34" s="117"/>
+      <c r="E34" s="118"/>
+    </row>
+    <row r="35" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B35" s="113" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="114">
         <v>6</v>
       </c>
-      <c r="D34" s="123"/>
-      <c r="E34" s="124"/>
-    </row>
-    <row r="35" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="119" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="120">
+      <c r="D35" s="117"/>
+      <c r="E35" s="118"/>
+    </row>
+    <row r="36" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="113" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="114">
         <v>6</v>
       </c>
-      <c r="D35" s="123"/>
-      <c r="E35" s="124"/>
-    </row>
-    <row r="36" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B36" s="119" t="s">
-        <v>120</v>
-      </c>
-      <c r="C36" s="120">
+      <c r="D36" s="117"/>
+      <c r="E36" s="118"/>
+    </row>
+    <row r="37" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B37" s="113" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37" s="114">
         <v>6</v>
       </c>
-      <c r="D36" s="123"/>
-      <c r="E36" s="124"/>
-    </row>
-    <row r="37" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="119" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="120">
+      <c r="D37" s="117"/>
+      <c r="E37" s="118"/>
+    </row>
+    <row r="38" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B38" s="113" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="114">
         <v>6</v>
       </c>
-      <c r="D37" s="123"/>
-      <c r="E37" s="124"/>
-    </row>
-    <row r="38" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="119" t="s">
-        <v>122</v>
-      </c>
-      <c r="C38" s="120">
+      <c r="D38" s="117"/>
+      <c r="E38" s="118"/>
+    </row>
+    <row r="39" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B39" s="113" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="114">
         <v>6</v>
       </c>
-      <c r="D38" s="123"/>
-      <c r="E38" s="124"/>
-    </row>
-    <row r="39" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="119" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="120">
+      <c r="D39" s="117"/>
+      <c r="E39" s="118"/>
+    </row>
+    <row r="40" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="113" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="114">
         <v>6</v>
       </c>
-      <c r="D39" s="123"/>
-      <c r="E39" s="124"/>
-    </row>
-    <row r="40" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B40" s="119" t="s">
-        <v>124</v>
-      </c>
-      <c r="C40" s="120">
+      <c r="D40" s="117"/>
+      <c r="E40" s="118"/>
+    </row>
+    <row r="41" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B41" s="113" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="114">
         <v>6</v>
       </c>
-      <c r="D40" s="123"/>
-      <c r="E40" s="124"/>
-    </row>
-    <row r="41" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B41" s="119" t="s">
-        <v>125</v>
-      </c>
-      <c r="C41" s="120">
+      <c r="D41" s="117"/>
+      <c r="E41" s="118"/>
+    </row>
+    <row r="42" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B42" s="113" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" s="114">
         <v>6</v>
       </c>
-      <c r="D41" s="123"/>
-      <c r="E41" s="124"/>
-    </row>
-    <row r="42" spans="2:5" ht="21" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="119" t="s">
-        <v>126</v>
-      </c>
-      <c r="C42" s="120">
+      <c r="D42" s="117"/>
+      <c r="E42" s="118"/>
+    </row>
+    <row r="43" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B43" s="119" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="114">
         <v>6</v>
       </c>
-      <c r="D42" s="123"/>
-      <c r="E42" s="124"/>
-    </row>
-    <row r="43" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B43" s="125" t="s">
-        <v>127</v>
-      </c>
-      <c r="C43" s="120">
+      <c r="D43" s="118"/>
+      <c r="E43" s="118"/>
+    </row>
+    <row r="44" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B44" s="119" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="114">
         <v>6</v>
       </c>
-      <c r="D43" s="124"/>
-      <c r="E43" s="124"/>
-    </row>
-    <row r="44" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B44" s="125" t="s">
-        <v>128</v>
-      </c>
-      <c r="C44" s="120">
+      <c r="D44" s="118"/>
+      <c r="E44" s="118"/>
+    </row>
+    <row r="45" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B45" s="119" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="114">
         <v>6</v>
       </c>
-      <c r="D44" s="124"/>
-      <c r="E44" s="124"/>
-    </row>
-    <row r="45" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B45" s="125" t="s">
-        <v>129</v>
-      </c>
-      <c r="C45" s="120">
+      <c r="D45" s="118"/>
+      <c r="E45" s="118"/>
+    </row>
+    <row r="46" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="119" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="114">
         <v>6</v>
       </c>
-      <c r="D45" s="124"/>
-      <c r="E45" s="124"/>
-    </row>
-    <row r="46" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="125" t="s">
-        <v>130</v>
-      </c>
-      <c r="C46" s="120">
+      <c r="D46" s="118"/>
+      <c r="E46" s="118"/>
+    </row>
+    <row r="47" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B47" s="119" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="114">
         <v>6</v>
       </c>
-      <c r="D46" s="124"/>
-      <c r="E46" s="124"/>
-    </row>
-    <row r="47" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B47" s="125" t="s">
-        <v>131</v>
-      </c>
-      <c r="C47" s="120">
+      <c r="D47" s="118"/>
+      <c r="E47" s="118"/>
+    </row>
+    <row r="48" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B48" s="119" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="114">
         <v>6</v>
       </c>
-      <c r="D47" s="124"/>
-      <c r="E47" s="124"/>
-    </row>
-    <row r="48" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B48" s="125" t="s">
-        <v>132</v>
-      </c>
-      <c r="C48" s="120">
+      <c r="D48" s="118"/>
+      <c r="E48" s="118"/>
+    </row>
+    <row r="49" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B49" s="119" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="114">
         <v>6</v>
       </c>
-      <c r="D48" s="124"/>
-      <c r="E48" s="124"/>
-    </row>
-    <row r="49" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B49" s="125" t="s">
-        <v>133</v>
-      </c>
-      <c r="C49" s="120">
+      <c r="D49" s="118"/>
+      <c r="E49" s="118"/>
+    </row>
+    <row r="50" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B50" s="119" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="114">
         <v>6</v>
       </c>
-      <c r="D49" s="124"/>
-      <c r="E49" s="124"/>
-    </row>
-    <row r="50" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B50" s="125" t="s">
-        <v>134</v>
-      </c>
-      <c r="C50" s="120">
+      <c r="D50" s="118"/>
+      <c r="E50" s="118"/>
+    </row>
+    <row r="51" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B51" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="114">
         <v>6</v>
       </c>
-      <c r="D50" s="124"/>
-      <c r="E50" s="124"/>
-    </row>
-    <row r="51" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B51" s="125" t="s">
-        <v>135</v>
-      </c>
-      <c r="C51" s="120">
+      <c r="D51" s="118"/>
+      <c r="E51" s="118"/>
+    </row>
+    <row r="52" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B52" s="119" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="114">
         <v>6</v>
       </c>
-      <c r="D51" s="124"/>
-      <c r="E51" s="124"/>
-    </row>
-    <row r="52" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B52" s="125" t="s">
-        <v>136</v>
-      </c>
-      <c r="C52" s="120">
+      <c r="D52" s="118"/>
+      <c r="E52" s="118"/>
+    </row>
+    <row r="53" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B53" s="119" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="114">
+        <v>2</v>
+      </c>
+      <c r="D53" s="118"/>
+      <c r="E53" s="118"/>
+    </row>
+    <row r="54" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B54" s="120" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" s="114">
         <v>6</v>
       </c>
-      <c r="D52" s="124"/>
-      <c r="E52" s="124"/>
-    </row>
-    <row r="53" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B53" s="125" t="s">
-        <v>137</v>
-      </c>
-      <c r="C53" s="120">
-        <v>2</v>
-      </c>
-      <c r="D53" s="124"/>
-      <c r="E53" s="124"/>
-    </row>
-    <row r="54" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B54" s="126" t="s">
-        <v>138</v>
-      </c>
-      <c r="C54" s="120">
+      <c r="D54" s="121"/>
+      <c r="E54" s="121"/>
+    </row>
+    <row r="55" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B55" s="120" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="114">
         <v>6</v>
       </c>
-      <c r="D54" s="127"/>
-      <c r="E54" s="127"/>
-    </row>
-    <row r="55" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B55" s="126" t="s">
-        <v>139</v>
-      </c>
-      <c r="C55" s="120">
+      <c r="D55" s="120"/>
+      <c r="E55" s="120"/>
+    </row>
+    <row r="56" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B56" s="120" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="122">
         <v>6</v>
       </c>
-      <c r="D55" s="126"/>
-      <c r="E55" s="126"/>
-    </row>
-    <row r="56" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B56" s="126" t="s">
-        <v>140</v>
-      </c>
-      <c r="C56" s="128">
-        <v>6</v>
-      </c>
-      <c r="D56" s="126"/>
-      <c r="E56" s="126"/>
+      <c r="D56" s="120"/>
+      <c r="E56" s="120"/>
     </row>
     <row r="57" spans="2:5" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="B57" s="129" t="s">
+      <c r="B57" s="123" t="s">
         <v>141</v>
       </c>
-      <c r="C57" s="130">
+      <c r="C57" s="124">
         <f>SUM(C9:C56)+C7</f>
         <v>290</v>
       </c>
-      <c r="D57" s="130">
+      <c r="D57" s="124">
         <f>SUM(D9:D56)+D7</f>
-        <v>107</v>
-      </c>
-      <c r="E57" s="129"/>
+        <v>113</v>
+      </c>
+      <c r="E57" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2819,7 +2843,7 @@
     <col min="13" max="13" width="15.7265625" style="15" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.08984375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="10.1796875" style="2" customWidth="1"/>
     <col min="17" max="17" width="17.81640625" style="2" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="15.7265625" style="15" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="14.453125" style="2" bestFit="1" customWidth="1"/>
@@ -2838,12 +2862,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:30" x14ac:dyDescent="0.9">
-      <c r="B1" s="141" t="s">
+      <c r="B1" s="157" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="141"/>
-      <c r="D1" s="141"/>
-      <c r="E1" s="141"/>
+      <c r="C1" s="157"/>
+      <c r="D1" s="157"/>
+      <c r="E1" s="157"/>
       <c r="F1" s="13"/>
       <c r="G1" s="14"/>
       <c r="K1" s="13"/>
@@ -2873,63 +2897,63 @@
         <v>45511</v>
       </c>
       <c r="C3" s="18">
-        <v>1285</v>
+        <f>D3-B3</f>
+        <v>753</v>
       </c>
       <c r="D3" s="19">
-        <f>B3+C3</f>
-        <v>46796</v>
+        <v>46264</v>
       </c>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
       <c r="G3" s="18">
         <f>C3/30.5</f>
-        <v>42.131147540983605</v>
+        <v>24.688524590163933</v>
       </c>
       <c r="V3" s="2"/>
     </row>
     <row r="4" spans="2:30" ht="22" thickBot="1" x14ac:dyDescent="0.95"/>
     <row r="5" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B5" s="142" t="s">
+      <c r="B5" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="144"/>
+      <c r="C5" s="159"/>
+      <c r="D5" s="159"/>
+      <c r="E5" s="160"/>
       <c r="F5" s="20"/>
-      <c r="G5" s="142" t="s">
+      <c r="G5" s="158" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="144"/>
+      <c r="H5" s="159"/>
+      <c r="I5" s="159"/>
+      <c r="J5" s="160"/>
       <c r="K5" s="20"/>
-      <c r="L5" s="145" t="s">
+      <c r="L5" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="M5" s="146"/>
-      <c r="N5" s="146"/>
-      <c r="O5" s="147"/>
+      <c r="M5" s="162"/>
+      <c r="N5" s="162"/>
+      <c r="O5" s="163"/>
       <c r="P5" s="20"/>
-      <c r="Q5" s="145" t="s">
+      <c r="Q5" s="161" t="s">
         <v>8</v>
       </c>
-      <c r="R5" s="146"/>
-      <c r="S5" s="146"/>
-      <c r="T5" s="147"/>
+      <c r="R5" s="162"/>
+      <c r="S5" s="162"/>
+      <c r="T5" s="163"/>
       <c r="U5" s="20"/>
-      <c r="V5" s="138" t="s">
+      <c r="V5" s="154" t="s">
         <v>9</v>
       </c>
-      <c r="W5" s="139"/>
-      <c r="X5" s="139"/>
-      <c r="Y5" s="140"/>
+      <c r="W5" s="155"/>
+      <c r="X5" s="155"/>
+      <c r="Y5" s="156"/>
       <c r="Z5" s="20"/>
-      <c r="AA5" s="138" t="s">
+      <c r="AA5" s="154" t="s">
         <v>10</v>
       </c>
-      <c r="AB5" s="139"/>
-      <c r="AC5" s="139"/>
-      <c r="AD5" s="140"/>
+      <c r="AB5" s="155"/>
+      <c r="AC5" s="155"/>
+      <c r="AD5" s="156"/>
     </row>
     <row r="6" spans="2:30" s="15" customFormat="1" ht="64.5" x14ac:dyDescent="0.9">
       <c r="B6" s="21"/>
@@ -4343,7 +4367,7 @@
         <v>46153</v>
       </c>
     </row>
-    <row r="22" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
+    <row r="22" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B22" s="35" t="s">
         <v>28</v>
       </c>
@@ -4404,19 +4428,19 @@
         <v>46142</v>
       </c>
       <c r="U22" s="34"/>
-      <c r="V22" s="45" t="s">
+      <c r="V22" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="W22" s="46">
+      <c r="W22" s="31">
         <f t="shared" si="6"/>
         <v>46173</v>
       </c>
-      <c r="X22" s="47">
-        <v>12</v>
-      </c>
-      <c r="Y22" s="48">
-        <f t="shared" si="14"/>
-        <v>46185</v>
+      <c r="X22" s="32">
+        <f>Y22-W22</f>
+        <v>19</v>
+      </c>
+      <c r="Y22" s="31">
+        <v>46192</v>
       </c>
       <c r="Z22" s="34"/>
       <c r="AA22" s="35" t="s">
@@ -4495,35 +4519,34 @@
         <v>46166</v>
       </c>
       <c r="U23" s="34"/>
-      <c r="V23" s="35" t="s">
+      <c r="V23" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="W23" s="49">
+      <c r="W23" s="60">
         <f t="shared" si="6"/>
-        <v>46185</v>
-      </c>
-      <c r="X23" s="50">
-        <v>12</v>
-      </c>
-      <c r="Y23" s="51">
+        <v>46192</v>
+      </c>
+      <c r="X23" s="61">
+        <v>12</v>
+      </c>
+      <c r="Y23" s="62">
         <f t="shared" si="14"/>
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="Z23" s="34"/>
-      <c r="AA23" s="45" t="s">
+      <c r="AA23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="AB23" s="46">
+      <c r="AB23" s="31">
         <f t="shared" si="7"/>
         <v>46173</v>
       </c>
-      <c r="AC23" s="47">
-        <f t="shared" ref="AC23:AC48" si="18">X23</f>
-        <v>12</v>
-      </c>
-      <c r="AD23" s="48">
-        <f t="shared" si="15"/>
-        <v>46185</v>
+      <c r="AC23" s="32">
+        <f>AD23-AB23</f>
+        <v>24</v>
+      </c>
+      <c r="AD23" s="31">
+        <v>46197</v>
       </c>
     </row>
     <row r="24" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
@@ -4572,50 +4595,50 @@
         <v>46173</v>
       </c>
       <c r="P24" s="34"/>
-      <c r="Q24" s="65" t="s">
+      <c r="Q24" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="R24" s="66">
+      <c r="R24" s="31">
         <f t="shared" si="12"/>
         <v>46166</v>
       </c>
-      <c r="S24" s="67">
-        <v>13</v>
-      </c>
-      <c r="T24" s="68">
-        <f t="shared" si="13"/>
-        <v>46179</v>
+      <c r="S24" s="32">
+        <f>T24-R24</f>
+        <v>36</v>
+      </c>
+      <c r="T24" s="31">
+        <v>46202</v>
       </c>
       <c r="U24" s="34"/>
       <c r="V24" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="W24" s="49">
+      <c r="W24" s="45">
         <f t="shared" si="6"/>
+        <v>46204</v>
+      </c>
+      <c r="X24" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y24" s="47">
+        <f t="shared" si="14"/>
+        <v>46216</v>
+      </c>
+      <c r="Z24" s="34"/>
+      <c r="AA24" s="59" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB24" s="60">
+        <f t="shared" si="7"/>
         <v>46197</v>
       </c>
-      <c r="X24" s="50">
-        <v>12</v>
-      </c>
-      <c r="Y24" s="51">
-        <f t="shared" si="14"/>
+      <c r="AC24" s="61">
+        <f t="shared" ref="AC24:AC40" si="18">X24</f>
+        <v>12</v>
+      </c>
+      <c r="AD24" s="62">
+        <f t="shared" si="15"/>
         <v>46209</v>
-      </c>
-      <c r="Z24" s="34"/>
-      <c r="AA24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB24" s="49">
-        <f t="shared" si="7"/>
-        <v>46185</v>
-      </c>
-      <c r="AC24" s="50">
-        <f t="shared" si="18"/>
-        <v>12</v>
-      </c>
-      <c r="AD24" s="51">
-        <f t="shared" si="15"/>
-        <v>46197</v>
       </c>
     </row>
     <row r="25" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
@@ -4649,69 +4672,69 @@
         <v>46133</v>
       </c>
       <c r="K25" s="41"/>
-      <c r="L25" s="65" t="s">
+      <c r="L25" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="M25" s="66">
+      <c r="M25" s="31">
         <f t="shared" si="10"/>
         <v>46173</v>
       </c>
-      <c r="N25" s="67">
-        <v>13</v>
-      </c>
-      <c r="O25" s="68">
-        <f t="shared" si="11"/>
-        <v>46186</v>
+      <c r="N25" s="32">
+        <f>O25-M25</f>
+        <v>29</v>
+      </c>
+      <c r="O25" s="31">
+        <v>46202</v>
       </c>
       <c r="P25" s="34"/>
-      <c r="Q25" s="38" t="s">
+      <c r="Q25" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="R25" s="59">
+      <c r="R25" s="60">
         <f t="shared" si="12"/>
-        <v>46179</v>
-      </c>
-      <c r="S25" s="56">
-        <v>12</v>
-      </c>
-      <c r="T25" s="60">
-        <f t="shared" si="13"/>
-        <v>46191</v>
+        <v>46202</v>
+      </c>
+      <c r="S25" s="61">
+        <v>12</v>
+      </c>
+      <c r="T25" s="62">
+        <f>S25+R25</f>
+        <v>46214</v>
       </c>
       <c r="U25" s="34"/>
       <c r="V25" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="W25" s="58">
+      <c r="W25" s="54">
         <f t="shared" si="6"/>
-        <v>46209</v>
-      </c>
-      <c r="X25" s="56">
-        <v>12</v>
-      </c>
-      <c r="Y25" s="55">
+        <v>46216</v>
+      </c>
+      <c r="X25" s="52">
+        <v>12</v>
+      </c>
+      <c r="Y25" s="51">
         <f t="shared" si="14"/>
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="Z25" s="34"/>
       <c r="AA25" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="AB25" s="58">
+      <c r="AB25" s="54">
         <f t="shared" si="7"/>
-        <v>46197</v>
-      </c>
-      <c r="AC25" s="56">
+        <v>46209</v>
+      </c>
+      <c r="AC25" s="52">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="AD25" s="55">
+      <c r="AD25" s="51">
         <f t="shared" si="15"/>
-        <v>46209</v>
+        <v>46221</v>
       </c>
     </row>
     <row r="26" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B26" s="61" t="s">
+      <c r="B26" s="35" t="s">
         <v>32</v>
       </c>
       <c r="C26" s="31">
@@ -4741,1099 +4764,1091 @@
         <v>46149</v>
       </c>
       <c r="K26" s="43"/>
-      <c r="L26" s="61" t="s">
+      <c r="L26" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="M26" s="69">
+      <c r="M26" s="60">
         <f t="shared" si="10"/>
-        <v>46186</v>
-      </c>
-      <c r="N26" s="63">
+        <v>46202</v>
+      </c>
+      <c r="N26" s="61">
         <v>12</v>
       </c>
       <c r="O26" s="62">
         <f t="shared" si="11"/>
-        <v>46198</v>
+        <v>46214</v>
       </c>
       <c r="P26" s="42"/>
-      <c r="Q26" s="61" t="s">
+      <c r="Q26" s="55" t="s">
         <v>32</v>
       </c>
-      <c r="R26" s="70">
+      <c r="R26" s="64">
         <f t="shared" si="12"/>
-        <v>46191</v>
-      </c>
-      <c r="S26" s="63">
-        <f t="shared" ref="S26:S49" si="19">N26</f>
-        <v>12</v>
-      </c>
-      <c r="T26" s="71">
+        <v>46214</v>
+      </c>
+      <c r="S26" s="57">
+        <v>11</v>
+      </c>
+      <c r="T26" s="65">
         <f t="shared" si="13"/>
-        <v>46203</v>
+        <v>46225</v>
       </c>
       <c r="U26" s="42"/>
-      <c r="V26" s="72" t="s">
+      <c r="V26" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="W26" s="69">
+      <c r="W26" s="63">
         <f t="shared" si="6"/>
+        <v>46228</v>
+      </c>
+      <c r="X26" s="57">
+        <f t="shared" ref="X26" si="19">S26</f>
+        <v>11</v>
+      </c>
+      <c r="Y26" s="56">
+        <f t="shared" si="14"/>
+        <v>46239</v>
+      </c>
+      <c r="Z26" s="42"/>
+      <c r="AA26" s="55" t="s">
+        <v>32</v>
+      </c>
+      <c r="AB26" s="63">
+        <f t="shared" si="7"/>
         <v>46221</v>
       </c>
-      <c r="X26" s="63">
-        <f t="shared" ref="X26" si="20">S26</f>
-        <v>12</v>
-      </c>
-      <c r="Y26" s="62">
-        <f t="shared" si="14"/>
-        <v>46233</v>
-      </c>
-      <c r="Z26" s="42"/>
-      <c r="AA26" s="61" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB26" s="69">
-        <f t="shared" si="7"/>
-        <v>46209</v>
-      </c>
-      <c r="AC26" s="63">
+      <c r="AC26" s="57">
         <f t="shared" si="18"/>
-        <v>12</v>
-      </c>
-      <c r="AD26" s="64">
+        <v>11</v>
+      </c>
+      <c r="AD26" s="58">
         <f t="shared" si="15"/>
-        <v>46221</v>
+        <v>46232</v>
       </c>
     </row>
     <row r="27" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B27" s="65" t="s">
+      <c r="B27" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="66">
+      <c r="C27" s="31">
         <f t="shared" si="8"/>
         <v>46170</v>
       </c>
-      <c r="D27" s="67">
-        <v>13</v>
-      </c>
-      <c r="E27" s="68">
-        <f t="shared" si="9"/>
-        <v>46183</v>
+      <c r="D27" s="32">
+        <f>E27-C27</f>
+        <v>24</v>
+      </c>
+      <c r="E27" s="33">
+        <v>46194</v>
       </c>
       <c r="F27" s="34"/>
-      <c r="G27" s="38" t="s">
+      <c r="G27" s="129" t="s">
         <v>33</v>
       </c>
       <c r="H27" s="39">
         <f t="shared" si="16"/>
         <v>46149</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="32">
         <v>17</v>
       </c>
-      <c r="J27" s="39">
+      <c r="J27" s="130">
         <f t="shared" si="17"/>
         <v>46166</v>
       </c>
-      <c r="K27" s="44"/>
-      <c r="L27" s="73" t="s">
+      <c r="K27" s="126"/>
+      <c r="L27" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="77">
+      <c r="M27" s="71">
         <f t="shared" si="10"/>
-        <v>46198</v>
-      </c>
-      <c r="N27" s="75">
-        <v>12</v>
-      </c>
-      <c r="O27" s="74">
+        <v>46214</v>
+      </c>
+      <c r="N27" s="69">
+        <v>12</v>
+      </c>
+      <c r="O27" s="68">
         <f t="shared" si="11"/>
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="P27" s="34"/>
-      <c r="Q27" s="73" t="s">
+      <c r="Q27" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="R27" s="78">
+      <c r="R27" s="72">
         <f t="shared" si="12"/>
-        <v>46203</v>
-      </c>
-      <c r="S27" s="75">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T27" s="79">
+        <v>46225</v>
+      </c>
+      <c r="S27" s="69">
+        <v>11</v>
+      </c>
+      <c r="T27" s="73">
         <f t="shared" si="13"/>
-        <v>46215</v>
+        <v>46236</v>
       </c>
       <c r="U27" s="34"/>
-      <c r="V27" s="80" t="s">
+      <c r="V27" s="74" t="s">
         <v>33</v>
       </c>
-      <c r="W27" s="77">
+      <c r="W27" s="71">
         <f t="shared" si="6"/>
-        <v>46233</v>
-      </c>
-      <c r="X27" s="75">
-        <v>12</v>
-      </c>
-      <c r="Y27" s="74">
+        <v>46239</v>
+      </c>
+      <c r="X27" s="69">
+        <v>12</v>
+      </c>
+      <c r="Y27" s="68">
         <f t="shared" si="14"/>
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="Z27" s="34"/>
-      <c r="AA27" s="73" t="s">
+      <c r="AA27" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="AB27" s="77">
+      <c r="AB27" s="71">
         <f t="shared" si="7"/>
-        <v>46221</v>
-      </c>
-      <c r="AC27" s="75">
+        <v>46232</v>
+      </c>
+      <c r="AC27" s="69">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="AD27" s="74">
+      <c r="AD27" s="68">
         <f t="shared" si="15"/>
-        <v>46233</v>
+        <v>46244</v>
       </c>
     </row>
     <row r="28" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B28" s="35" t="s">
+      <c r="B28" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="C28" s="51">
+      <c r="C28" s="60">
         <f t="shared" si="8"/>
-        <v>46183</v>
-      </c>
-      <c r="D28" s="50">
+        <v>46194</v>
+      </c>
+      <c r="D28" s="61">
         <v>13</v>
       </c>
-      <c r="E28" s="81">
+      <c r="E28" s="62">
         <f t="shared" si="9"/>
-        <v>46196</v>
+        <v>46207</v>
       </c>
       <c r="F28" s="34"/>
-      <c r="G28" s="65" t="s">
+      <c r="G28" s="127" t="s">
         <v>34</v>
       </c>
-      <c r="H28" s="66">
+      <c r="H28" s="128">
         <f t="shared" si="16"/>
         <v>46166</v>
       </c>
-      <c r="I28" s="67">
-        <f t="shared" ref="I28:I50" si="21">D28</f>
-        <v>13</v>
-      </c>
-      <c r="J28" s="68">
-        <f t="shared" si="17"/>
-        <v>46179</v>
+      <c r="I28" s="32">
+        <f>J28-H28</f>
+        <v>26</v>
+      </c>
+      <c r="J28" s="128">
+        <v>46192</v>
       </c>
       <c r="K28" s="37"/>
       <c r="L28" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="M28" s="49">
+      <c r="M28" s="45">
         <f t="shared" si="10"/>
-        <v>46210</v>
-      </c>
-      <c r="N28" s="50">
-        <v>12</v>
-      </c>
-      <c r="O28" s="51">
+        <v>46226</v>
+      </c>
+      <c r="N28" s="46">
+        <v>12</v>
+      </c>
+      <c r="O28" s="47">
         <f t="shared" si="11"/>
-        <v>46222</v>
+        <v>46238</v>
       </c>
       <c r="P28" s="34"/>
       <c r="Q28" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="R28" s="52">
+      <c r="R28" s="48">
         <f t="shared" si="12"/>
-        <v>46215</v>
-      </c>
-      <c r="S28" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T28" s="53">
+        <v>46236</v>
+      </c>
+      <c r="S28" s="46">
+        <v>11</v>
+      </c>
+      <c r="T28" s="49">
         <f t="shared" si="13"/>
-        <v>46227</v>
+        <v>46247</v>
       </c>
       <c r="U28" s="34"/>
-      <c r="V28" s="82" t="s">
+      <c r="V28" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="W28" s="49">
+      <c r="W28" s="45">
         <f t="shared" si="6"/>
-        <v>46245</v>
-      </c>
-      <c r="X28" s="50">
-        <v>12</v>
-      </c>
-      <c r="Y28" s="51">
+        <v>46251</v>
+      </c>
+      <c r="X28" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y28" s="47">
         <f t="shared" si="14"/>
-        <v>46257</v>
+        <v>46263</v>
       </c>
       <c r="Z28" s="34"/>
       <c r="AA28" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="AB28" s="49">
+      <c r="AB28" s="45">
         <f t="shared" si="7"/>
-        <v>46233</v>
-      </c>
-      <c r="AC28" s="50">
+        <v>46244</v>
+      </c>
+      <c r="AC28" s="46">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="AD28" s="51">
+      <c r="AD28" s="47">
         <f t="shared" si="15"/>
-        <v>46245</v>
-      </c>
-    </row>
-    <row r="29" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
+        <v>46256</v>
+      </c>
+    </row>
+    <row r="29" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B29" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="51">
+      <c r="C29" s="47">
         <f t="shared" si="8"/>
-        <v>46196</v>
-      </c>
-      <c r="D29" s="50">
-        <v>14</v>
-      </c>
-      <c r="E29" s="81">
+        <v>46207</v>
+      </c>
+      <c r="D29" s="46">
+        <v>12</v>
+      </c>
+      <c r="E29" s="75">
         <f t="shared" si="9"/>
-        <v>46210</v>
+        <v>46219</v>
       </c>
       <c r="F29" s="34"/>
-      <c r="G29" s="35" t="s">
+      <c r="G29" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="51">
+      <c r="H29" s="60">
         <f t="shared" si="16"/>
-        <v>46179</v>
-      </c>
-      <c r="I29" s="50">
-        <f t="shared" si="21"/>
-        <v>14</v>
-      </c>
-      <c r="J29" s="51">
+        <v>46192</v>
+      </c>
+      <c r="I29" s="61">
+        <f t="shared" ref="I29:I50" si="20">D29</f>
+        <v>12</v>
+      </c>
+      <c r="J29" s="62">
         <f t="shared" si="17"/>
-        <v>46193</v>
+        <v>46204</v>
       </c>
       <c r="K29" s="37"/>
       <c r="L29" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="M29" s="49">
+      <c r="M29" s="45">
         <f t="shared" si="10"/>
-        <v>46222</v>
-      </c>
-      <c r="N29" s="50">
-        <v>14</v>
-      </c>
-      <c r="O29" s="51">
+        <v>46238</v>
+      </c>
+      <c r="N29" s="46">
+        <v>13</v>
+      </c>
+      <c r="O29" s="47">
         <f t="shared" si="11"/>
-        <v>46236</v>
+        <v>46251</v>
       </c>
       <c r="P29" s="34"/>
       <c r="Q29" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="R29" s="52">
+      <c r="R29" s="48">
         <f t="shared" si="12"/>
-        <v>46227</v>
-      </c>
-      <c r="S29" s="50">
-        <v>12</v>
-      </c>
-      <c r="T29" s="53">
+        <v>46247</v>
+      </c>
+      <c r="S29" s="46">
+        <v>11</v>
+      </c>
+      <c r="T29" s="49">
         <f t="shared" si="13"/>
-        <v>46239</v>
+        <v>46258</v>
       </c>
       <c r="U29" s="34"/>
-      <c r="V29" s="82" t="s">
+      <c r="V29" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="W29" s="49">
+      <c r="W29" s="45">
         <f t="shared" si="6"/>
-        <v>46257</v>
-      </c>
-      <c r="X29" s="50">
-        <v>12</v>
-      </c>
-      <c r="Y29" s="51">
+        <v>46263</v>
+      </c>
+      <c r="X29" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y29" s="47">
         <f t="shared" si="14"/>
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="Z29" s="34"/>
       <c r="AA29" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="AB29" s="49">
+      <c r="AB29" s="45">
         <f t="shared" si="7"/>
-        <v>46245</v>
-      </c>
-      <c r="AC29" s="50">
+        <v>46256</v>
+      </c>
+      <c r="AC29" s="46">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="AD29" s="51">
+      <c r="AD29" s="47">
         <f t="shared" si="15"/>
-        <v>46257</v>
+        <v>46268</v>
       </c>
     </row>
     <row r="30" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B30" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="47">
         <f t="shared" si="8"/>
-        <v>46210</v>
-      </c>
-      <c r="D30" s="50">
-        <v>13</v>
-      </c>
-      <c r="E30" s="81">
+        <v>46219</v>
+      </c>
+      <c r="D30" s="46">
+        <v>12</v>
+      </c>
+      <c r="E30" s="75">
         <f t="shared" si="9"/>
-        <v>46223</v>
+        <v>46231</v>
       </c>
       <c r="F30" s="34"/>
       <c r="G30" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="51">
+      <c r="H30" s="47">
         <f t="shared" si="16"/>
-        <v>46193</v>
-      </c>
-      <c r="I30" s="50">
-        <f t="shared" si="21"/>
+        <v>46204</v>
+      </c>
+      <c r="I30" s="46">
         <v>13</v>
       </c>
-      <c r="J30" s="51">
+      <c r="J30" s="47">
         <f t="shared" si="17"/>
-        <v>46206</v>
+        <v>46217</v>
       </c>
       <c r="K30" s="37"/>
       <c r="L30" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="M30" s="49">
+      <c r="M30" s="45">
         <f t="shared" si="10"/>
-        <v>46236</v>
-      </c>
-      <c r="N30" s="50">
-        <v>12</v>
-      </c>
-      <c r="O30" s="51">
+        <v>46251</v>
+      </c>
+      <c r="N30" s="46">
+        <v>12</v>
+      </c>
+      <c r="O30" s="47">
         <f t="shared" si="11"/>
-        <v>46248</v>
+        <v>46263</v>
       </c>
       <c r="P30" s="34"/>
       <c r="Q30" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="R30" s="52">
+      <c r="R30" s="48">
         <f t="shared" si="12"/>
-        <v>46239</v>
-      </c>
-      <c r="S30" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T30" s="53">
+        <v>46258</v>
+      </c>
+      <c r="S30" s="46">
+        <v>11</v>
+      </c>
+      <c r="T30" s="49">
         <f t="shared" si="13"/>
-        <v>46251</v>
+        <v>46269</v>
       </c>
       <c r="U30" s="34"/>
-      <c r="V30" s="82" t="s">
+      <c r="V30" s="76" t="s">
         <v>36</v>
       </c>
-      <c r="W30" s="49">
+      <c r="W30" s="45">
         <f t="shared" si="6"/>
-        <v>46269</v>
-      </c>
-      <c r="X30" s="50">
-        <v>12</v>
-      </c>
-      <c r="Y30" s="51">
+        <v>46275</v>
+      </c>
+      <c r="X30" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y30" s="47">
         <f t="shared" si="14"/>
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="Z30" s="34"/>
       <c r="AA30" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="AB30" s="49">
+      <c r="AB30" s="45">
         <f t="shared" si="7"/>
-        <v>46257</v>
-      </c>
-      <c r="AC30" s="50">
+        <v>46268</v>
+      </c>
+      <c r="AC30" s="46">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="AD30" s="51">
+      <c r="AD30" s="47">
         <f t="shared" si="15"/>
-        <v>46269</v>
+        <v>46280</v>
       </c>
     </row>
     <row r="31" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B31" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="51">
+      <c r="C31" s="47">
         <f t="shared" si="8"/>
-        <v>46223</v>
-      </c>
-      <c r="D31" s="50">
-        <v>13</v>
-      </c>
-      <c r="E31" s="81">
+        <v>46231</v>
+      </c>
+      <c r="D31" s="46">
+        <v>12</v>
+      </c>
+      <c r="E31" s="75">
         <f t="shared" si="9"/>
-        <v>46236</v>
+        <v>46243</v>
       </c>
       <c r="F31" s="34"/>
       <c r="G31" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="H31" s="51">
+      <c r="H31" s="47">
         <f t="shared" si="16"/>
-        <v>46206</v>
-      </c>
-      <c r="I31" s="50">
-        <v>14</v>
-      </c>
-      <c r="J31" s="51">
+        <v>46217</v>
+      </c>
+      <c r="I31" s="46">
+        <v>13</v>
+      </c>
+      <c r="J31" s="47">
         <f t="shared" si="17"/>
-        <v>46220</v>
+        <v>46230</v>
       </c>
       <c r="K31" s="37"/>
       <c r="L31" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="M31" s="49">
+      <c r="M31" s="45">
         <f t="shared" si="10"/>
-        <v>46248</v>
-      </c>
-      <c r="N31" s="50">
-        <v>12</v>
-      </c>
-      <c r="O31" s="51">
+        <v>46263</v>
+      </c>
+      <c r="N31" s="46">
+        <v>12</v>
+      </c>
+      <c r="O31" s="47">
         <f t="shared" si="11"/>
-        <v>46260</v>
+        <v>46275</v>
       </c>
       <c r="P31" s="34"/>
       <c r="Q31" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="R31" s="52">
+      <c r="R31" s="48">
         <f t="shared" si="12"/>
-        <v>46251</v>
-      </c>
-      <c r="S31" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T31" s="53">
+        <v>46269</v>
+      </c>
+      <c r="S31" s="46">
+        <v>11</v>
+      </c>
+      <c r="T31" s="49">
         <f t="shared" si="13"/>
-        <v>46263</v>
+        <v>46280</v>
       </c>
       <c r="U31" s="34"/>
-      <c r="V31" s="82" t="s">
+      <c r="V31" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="W31" s="49">
+      <c r="W31" s="45">
         <f t="shared" si="6"/>
-        <v>46281</v>
-      </c>
-      <c r="X31" s="50">
-        <v>12</v>
-      </c>
-      <c r="Y31" s="51">
+        <v>46287</v>
+      </c>
+      <c r="X31" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y31" s="47">
         <f t="shared" si="14"/>
-        <v>46293</v>
+        <v>46299</v>
       </c>
       <c r="Z31" s="34"/>
       <c r="AA31" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="AB31" s="49">
+      <c r="AB31" s="45">
         <f t="shared" si="7"/>
-        <v>46269</v>
-      </c>
-      <c r="AC31" s="50">
+        <v>46280</v>
+      </c>
+      <c r="AC31" s="46">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="AD31" s="51">
+      <c r="AD31" s="47">
         <f t="shared" si="15"/>
-        <v>46281</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="32" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="C32" s="51">
+      <c r="C32" s="47">
         <f t="shared" si="8"/>
-        <v>46236</v>
-      </c>
-      <c r="D32" s="50">
-        <v>13</v>
-      </c>
-      <c r="E32" s="81">
+        <v>46243</v>
+      </c>
+      <c r="D32" s="46">
+        <v>12</v>
+      </c>
+      <c r="E32" s="75">
         <f t="shared" si="9"/>
-        <v>46249</v>
+        <v>46255</v>
       </c>
       <c r="F32" s="34"/>
       <c r="G32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="H32" s="51">
+      <c r="H32" s="47">
         <f t="shared" si="16"/>
-        <v>46220</v>
-      </c>
-      <c r="I32" s="50">
-        <v>14</v>
-      </c>
-      <c r="J32" s="51">
+        <v>46230</v>
+      </c>
+      <c r="I32" s="46">
+        <v>13</v>
+      </c>
+      <c r="J32" s="47">
         <f t="shared" si="17"/>
-        <v>46234</v>
+        <v>46243</v>
       </c>
       <c r="K32" s="37"/>
       <c r="L32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="M32" s="49">
+      <c r="M32" s="45">
         <f t="shared" si="10"/>
-        <v>46260</v>
-      </c>
-      <c r="N32" s="50">
-        <v>12</v>
-      </c>
-      <c r="O32" s="51">
+        <v>46275</v>
+      </c>
+      <c r="N32" s="46">
+        <v>12</v>
+      </c>
+      <c r="O32" s="47">
         <f t="shared" si="11"/>
-        <v>46272</v>
+        <v>46287</v>
       </c>
       <c r="P32" s="34"/>
       <c r="Q32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="R32" s="49">
+      <c r="R32" s="45">
         <f t="shared" si="12"/>
-        <v>46263</v>
-      </c>
-      <c r="S32" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T32" s="51">
+        <v>46280</v>
+      </c>
+      <c r="S32" s="46">
+        <v>11</v>
+      </c>
+      <c r="T32" s="47">
         <f t="shared" si="13"/>
-        <v>46275</v>
+        <v>46291</v>
       </c>
       <c r="U32" s="34"/>
-      <c r="V32" s="82" t="s">
+      <c r="V32" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="W32" s="49">
+      <c r="W32" s="45">
         <f t="shared" si="6"/>
-        <v>46293</v>
-      </c>
-      <c r="X32" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y32" s="51">
+        <v>46299</v>
+      </c>
+      <c r="X32" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y32" s="47">
         <f t="shared" si="14"/>
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="Z32" s="34"/>
       <c r="AA32" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="AB32" s="49">
+      <c r="AB32" s="45">
         <f t="shared" si="7"/>
-        <v>46281</v>
-      </c>
-      <c r="AC32" s="50">
-        <v>12</v>
-      </c>
-      <c r="AD32" s="51">
+        <v>46292</v>
+      </c>
+      <c r="AC32" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD32" s="47">
         <f t="shared" si="15"/>
-        <v>46293</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="33" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B33" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="51">
+      <c r="C33" s="47">
         <f t="shared" si="8"/>
-        <v>46249</v>
-      </c>
-      <c r="D33" s="50">
-        <v>13</v>
-      </c>
-      <c r="E33" s="81">
+        <v>46255</v>
+      </c>
+      <c r="D33" s="46">
+        <v>12</v>
+      </c>
+      <c r="E33" s="75">
         <f t="shared" si="9"/>
-        <v>46262</v>
+        <v>46267</v>
       </c>
       <c r="F33" s="34"/>
       <c r="G33" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="H33" s="51">
+      <c r="H33" s="47">
         <f t="shared" si="16"/>
-        <v>46234</v>
-      </c>
-      <c r="I33" s="50">
-        <v>14</v>
-      </c>
-      <c r="J33" s="51">
+        <v>46243</v>
+      </c>
+      <c r="I33" s="46">
+        <v>13</v>
+      </c>
+      <c r="J33" s="47">
         <f t="shared" si="17"/>
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="K33" s="37"/>
       <c r="L33" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="M33" s="49">
+      <c r="M33" s="45">
         <f t="shared" si="10"/>
-        <v>46272</v>
-      </c>
-      <c r="N33" s="50">
-        <v>12</v>
-      </c>
-      <c r="O33" s="51">
+        <v>46287</v>
+      </c>
+      <c r="N33" s="46">
+        <v>12</v>
+      </c>
+      <c r="O33" s="47">
         <f t="shared" si="11"/>
-        <v>46284</v>
+        <v>46299</v>
       </c>
       <c r="P33" s="34"/>
       <c r="Q33" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="R33" s="49">
+      <c r="R33" s="45">
         <f t="shared" si="12"/>
-        <v>46275</v>
-      </c>
-      <c r="S33" s="50">
-        <v>12</v>
-      </c>
-      <c r="T33" s="51">
+        <v>46291</v>
+      </c>
+      <c r="S33" s="46">
+        <v>12</v>
+      </c>
+      <c r="T33" s="47">
         <f t="shared" si="13"/>
-        <v>46287</v>
+        <v>46303</v>
       </c>
       <c r="U33" s="34"/>
-      <c r="V33" s="82" t="s">
+      <c r="V33" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="W33" s="49">
+      <c r="W33" s="45">
         <f t="shared" si="6"/>
-        <v>46304</v>
-      </c>
-      <c r="X33" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y33" s="51">
+        <v>46311</v>
+      </c>
+      <c r="X33" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y33" s="47">
         <f t="shared" si="14"/>
-        <v>46315</v>
+        <v>46323</v>
       </c>
       <c r="Z33" s="34"/>
       <c r="AA33" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="AB33" s="49">
+      <c r="AB33" s="45">
         <f t="shared" si="7"/>
-        <v>46293</v>
-      </c>
-      <c r="AC33" s="50">
-        <v>12</v>
-      </c>
-      <c r="AD33" s="51">
+        <v>46304</v>
+      </c>
+      <c r="AC33" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD33" s="47">
         <f t="shared" si="15"/>
-        <v>46305</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="34" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="51">
+      <c r="C34" s="47">
         <f t="shared" si="8"/>
-        <v>46262</v>
-      </c>
-      <c r="D34" s="50">
-        <v>13</v>
-      </c>
-      <c r="E34" s="81">
+        <v>46267</v>
+      </c>
+      <c r="D34" s="46">
+        <v>12</v>
+      </c>
+      <c r="E34" s="75">
         <f t="shared" si="9"/>
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="F34" s="34"/>
       <c r="G34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="H34" s="51">
+      <c r="H34" s="47">
         <f t="shared" si="16"/>
-        <v>46248</v>
-      </c>
-      <c r="I34" s="50">
-        <v>14</v>
-      </c>
-      <c r="J34" s="51">
+        <v>46256</v>
+      </c>
+      <c r="I34" s="46">
+        <v>13</v>
+      </c>
+      <c r="J34" s="47">
         <f t="shared" si="17"/>
-        <v>46262</v>
+        <v>46269</v>
       </c>
       <c r="K34" s="37"/>
       <c r="L34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="M34" s="49">
+      <c r="M34" s="45">
         <f t="shared" si="10"/>
-        <v>46284</v>
-      </c>
-      <c r="N34" s="50">
-        <v>12</v>
-      </c>
-      <c r="O34" s="51">
+        <v>46299</v>
+      </c>
+      <c r="N34" s="46">
+        <v>12</v>
+      </c>
+      <c r="O34" s="47">
         <f t="shared" si="11"/>
-        <v>46296</v>
+        <v>46311</v>
       </c>
       <c r="P34" s="34"/>
       <c r="Q34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="R34" s="49">
+      <c r="R34" s="45">
         <f t="shared" si="12"/>
-        <v>46287</v>
-      </c>
-      <c r="S34" s="50">
-        <v>12</v>
-      </c>
-      <c r="T34" s="51">
+        <v>46303</v>
+      </c>
+      <c r="S34" s="46">
+        <v>12</v>
+      </c>
+      <c r="T34" s="47">
         <f t="shared" si="13"/>
-        <v>46299</v>
+        <v>46315</v>
       </c>
       <c r="U34" s="34"/>
-      <c r="V34" s="82" t="s">
+      <c r="V34" s="76" t="s">
         <v>40</v>
       </c>
-      <c r="W34" s="49">
+      <c r="W34" s="45">
         <f t="shared" si="6"/>
-        <v>46315</v>
-      </c>
-      <c r="X34" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y34" s="51">
+        <v>46323</v>
+      </c>
+      <c r="X34" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y34" s="47">
         <f t="shared" si="14"/>
-        <v>46326</v>
+        <v>46335</v>
       </c>
       <c r="Z34" s="34"/>
       <c r="AA34" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="AB34" s="49">
+      <c r="AB34" s="45">
         <f t="shared" si="7"/>
-        <v>46305</v>
-      </c>
-      <c r="AC34" s="50">
+        <v>46316</v>
+      </c>
+      <c r="AC34" s="46">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD34" s="51">
+        <v>12</v>
+      </c>
+      <c r="AD34" s="47">
         <f t="shared" si="15"/>
-        <v>46316</v>
+        <v>46328</v>
       </c>
     </row>
     <row r="35" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B35" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="C35" s="55">
+      <c r="C35" s="51">
         <f t="shared" si="8"/>
-        <v>46275</v>
-      </c>
-      <c r="D35" s="56">
-        <v>13</v>
-      </c>
-      <c r="E35" s="57">
+        <v>46279</v>
+      </c>
+      <c r="D35" s="52">
+        <v>12</v>
+      </c>
+      <c r="E35" s="53">
         <f t="shared" si="9"/>
-        <v>46288</v>
+        <v>46291</v>
       </c>
       <c r="F35" s="34"/>
       <c r="G35" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="H35" s="55">
+      <c r="H35" s="51">
         <f t="shared" si="16"/>
-        <v>46262</v>
-      </c>
-      <c r="I35" s="56">
-        <v>14</v>
-      </c>
-      <c r="J35" s="55">
+        <v>46269</v>
+      </c>
+      <c r="I35" s="52">
+        <v>13</v>
+      </c>
+      <c r="J35" s="51">
         <f t="shared" si="17"/>
-        <v>46276</v>
+        <v>46282</v>
       </c>
       <c r="K35" s="41"/>
       <c r="L35" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="M35" s="58">
+      <c r="M35" s="54">
         <f t="shared" si="10"/>
-        <v>46296</v>
-      </c>
-      <c r="N35" s="56">
-        <v>12</v>
-      </c>
-      <c r="O35" s="55">
+        <v>46311</v>
+      </c>
+      <c r="N35" s="52">
+        <v>12</v>
+      </c>
+      <c r="O35" s="51">
         <f t="shared" si="11"/>
-        <v>46308</v>
+        <v>46323</v>
       </c>
       <c r="P35" s="34"/>
       <c r="Q35" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="R35" s="58">
+      <c r="R35" s="54">
         <f t="shared" si="12"/>
-        <v>46299</v>
-      </c>
-      <c r="S35" s="56">
-        <v>12</v>
-      </c>
-      <c r="T35" s="55">
+        <v>46315</v>
+      </c>
+      <c r="S35" s="52">
+        <v>12</v>
+      </c>
+      <c r="T35" s="51">
         <f t="shared" si="13"/>
-        <v>46311</v>
+        <v>46327</v>
       </c>
       <c r="U35" s="34"/>
-      <c r="V35" s="83" t="s">
+      <c r="V35" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="W35" s="58">
+      <c r="W35" s="54">
         <f t="shared" si="6"/>
-        <v>46326</v>
-      </c>
-      <c r="X35" s="56">
-        <v>11</v>
-      </c>
-      <c r="Y35" s="55">
+        <v>46335</v>
+      </c>
+      <c r="X35" s="52">
+        <v>12</v>
+      </c>
+      <c r="Y35" s="51">
         <f t="shared" si="14"/>
-        <v>46337</v>
+        <v>46347</v>
       </c>
       <c r="Z35" s="34"/>
       <c r="AA35" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="AB35" s="58">
+      <c r="AB35" s="54">
         <f t="shared" si="7"/>
-        <v>46316</v>
-      </c>
-      <c r="AC35" s="56">
+        <v>46328</v>
+      </c>
+      <c r="AC35" s="52">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD35" s="55">
+        <v>12</v>
+      </c>
+      <c r="AD35" s="51">
         <f t="shared" si="15"/>
+        <v>46340</v>
+      </c>
+    </row>
+    <row r="36" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B36" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" s="56">
+        <f t="shared" si="8"/>
+        <v>46291</v>
+      </c>
+      <c r="D36" s="57">
+        <v>12</v>
+      </c>
+      <c r="E36" s="58">
+        <f t="shared" si="9"/>
+        <v>46303</v>
+      </c>
+      <c r="F36" s="42"/>
+      <c r="G36" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H36" s="56">
+        <f t="shared" si="16"/>
+        <v>46282</v>
+      </c>
+      <c r="I36" s="57">
+        <v>12</v>
+      </c>
+      <c r="J36" s="58">
+        <f t="shared" si="17"/>
+        <v>46294</v>
+      </c>
+      <c r="K36" s="78"/>
+      <c r="L36" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="M36" s="63">
+        <f t="shared" si="10"/>
+        <v>46323</v>
+      </c>
+      <c r="N36" s="57">
+        <v>12</v>
+      </c>
+      <c r="O36" s="56">
+        <f t="shared" si="11"/>
+        <v>46335</v>
+      </c>
+      <c r="P36" s="42"/>
+      <c r="Q36" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="R36" s="63">
+        <f t="shared" si="12"/>
         <v>46327</v>
       </c>
-    </row>
-    <row r="36" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B36" s="61" t="s">
+      <c r="S36" s="57">
+        <v>12</v>
+      </c>
+      <c r="T36" s="56">
+        <f t="shared" si="13"/>
+        <v>46339</v>
+      </c>
+      <c r="U36" s="42"/>
+      <c r="V36" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="C36" s="62">
+      <c r="W36" s="63">
+        <f t="shared" si="6"/>
+        <v>46347</v>
+      </c>
+      <c r="X36" s="57">
+        <v>12</v>
+      </c>
+      <c r="Y36" s="56">
+        <f t="shared" si="14"/>
+        <v>46359</v>
+      </c>
+      <c r="Z36" s="42"/>
+      <c r="AA36" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB36" s="63">
+        <f t="shared" si="7"/>
+        <v>46340</v>
+      </c>
+      <c r="AC36" s="57">
+        <f t="shared" si="18"/>
+        <v>12</v>
+      </c>
+      <c r="AD36" s="58">
+        <f t="shared" si="15"/>
+        <v>46352</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
+      <c r="B37" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" s="68">
         <f t="shared" si="8"/>
-        <v>46288</v>
-      </c>
-      <c r="D36" s="63">
-        <v>13</v>
-      </c>
-      <c r="E36" s="64">
+        <v>46303</v>
+      </c>
+      <c r="D37" s="69">
+        <v>12</v>
+      </c>
+      <c r="E37" s="70">
         <f t="shared" si="9"/>
-        <v>46301</v>
-      </c>
-      <c r="F36" s="42"/>
-      <c r="G36" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="H36" s="62">
+        <v>46315</v>
+      </c>
+      <c r="F37" s="34"/>
+      <c r="G37" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="H37" s="68">
         <f t="shared" si="16"/>
-        <v>46276</v>
-      </c>
-      <c r="I36" s="63">
-        <v>14</v>
-      </c>
-      <c r="J36" s="64">
+        <v>46294</v>
+      </c>
+      <c r="I37" s="69">
+        <v>12</v>
+      </c>
+      <c r="J37" s="68">
         <f t="shared" si="17"/>
-        <v>46290</v>
-      </c>
-      <c r="K36" s="84"/>
-      <c r="L36" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="M36" s="69">
+        <v>46306</v>
+      </c>
+      <c r="K37" s="44"/>
+      <c r="L37" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="M37" s="71">
         <f t="shared" si="10"/>
-        <v>46308</v>
-      </c>
-      <c r="N36" s="63">
-        <v>12</v>
-      </c>
-      <c r="O36" s="62">
+        <v>46335</v>
+      </c>
+      <c r="N37" s="69">
+        <v>12</v>
+      </c>
+      <c r="O37" s="68">
         <f t="shared" si="11"/>
-        <v>46320</v>
-      </c>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="R36" s="69">
+        <v>46347</v>
+      </c>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="R37" s="71">
         <f t="shared" si="12"/>
-        <v>46311</v>
-      </c>
-      <c r="S36" s="63">
-        <v>12</v>
-      </c>
-      <c r="T36" s="62">
+        <v>46339</v>
+      </c>
+      <c r="S37" s="69">
+        <v>12</v>
+      </c>
+      <c r="T37" s="68">
         <f t="shared" si="13"/>
-        <v>46323</v>
-      </c>
-      <c r="U36" s="42"/>
-      <c r="V36" s="72" t="s">
-        <v>42</v>
-      </c>
-      <c r="W36" s="69">
+        <v>46351</v>
+      </c>
+      <c r="U37" s="34"/>
+      <c r="V37" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="W37" s="71">
         <f t="shared" si="6"/>
-        <v>46337</v>
-      </c>
-      <c r="X36" s="63">
-        <v>12</v>
-      </c>
-      <c r="Y36" s="62">
+        <v>46359</v>
+      </c>
+      <c r="X37" s="69">
+        <v>12</v>
+      </c>
+      <c r="Y37" s="68">
         <f t="shared" si="14"/>
-        <v>46349</v>
-      </c>
-      <c r="Z36" s="42"/>
-      <c r="AA36" s="61" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB36" s="69">
+        <v>46371</v>
+      </c>
+      <c r="Z37" s="34"/>
+      <c r="AA37" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB37" s="71">
         <f t="shared" si="7"/>
-        <v>46327</v>
-      </c>
-      <c r="AC36" s="63">
+        <v>46352</v>
+      </c>
+      <c r="AC37" s="69">
         <f t="shared" si="18"/>
         <v>12</v>
       </c>
-      <c r="AD36" s="64">
+      <c r="AD37" s="68">
         <f t="shared" si="15"/>
-        <v>46339</v>
-      </c>
-    </row>
-    <row r="37" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
-      <c r="B37" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" s="74">
-        <f t="shared" si="8"/>
-        <v>46301</v>
-      </c>
-      <c r="D37" s="75">
-        <v>13</v>
-      </c>
-      <c r="E37" s="76">
-        <f t="shared" si="9"/>
-        <v>46314</v>
-      </c>
-      <c r="F37" s="34"/>
-      <c r="G37" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="H37" s="74">
-        <f t="shared" si="16"/>
-        <v>46290</v>
-      </c>
-      <c r="I37" s="75">
-        <v>14</v>
-      </c>
-      <c r="J37" s="74">
-        <f t="shared" si="17"/>
-        <v>46304</v>
-      </c>
-      <c r="K37" s="44"/>
-      <c r="L37" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="M37" s="77">
-        <f t="shared" si="10"/>
-        <v>46320</v>
-      </c>
-      <c r="N37" s="75">
-        <v>12</v>
-      </c>
-      <c r="O37" s="74">
-        <f t="shared" si="11"/>
-        <v>46332</v>
-      </c>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="R37" s="77">
-        <f t="shared" si="12"/>
-        <v>46323</v>
-      </c>
-      <c r="S37" s="75">
-        <v>12</v>
-      </c>
-      <c r="T37" s="74">
-        <f t="shared" si="13"/>
-        <v>46335</v>
-      </c>
-      <c r="U37" s="34"/>
-      <c r="V37" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="W37" s="77">
-        <f t="shared" si="6"/>
-        <v>46349</v>
-      </c>
-      <c r="X37" s="75">
-        <v>11</v>
-      </c>
-      <c r="Y37" s="74">
-        <f t="shared" si="14"/>
-        <v>46360</v>
-      </c>
-      <c r="Z37" s="34"/>
-      <c r="AA37" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="AB37" s="77">
-        <f t="shared" si="7"/>
-        <v>46339</v>
-      </c>
-      <c r="AC37" s="75">
-        <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD37" s="74">
-        <f t="shared" si="15"/>
-        <v>46350</v>
+        <v>46364</v>
       </c>
     </row>
     <row r="38" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B38" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="C38" s="51">
+      <c r="C38" s="47">
         <f t="shared" si="8"/>
-        <v>46314</v>
-      </c>
-      <c r="D38" s="50">
-        <v>15</v>
-      </c>
-      <c r="E38" s="81">
+        <v>46315</v>
+      </c>
+      <c r="D38" s="46">
+        <v>14</v>
+      </c>
+      <c r="E38" s="75">
         <f t="shared" si="9"/>
         <v>46329</v>
       </c>
@@ -5841,1018 +5856,1006 @@
       <c r="G38" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="H38" s="51">
+      <c r="H38" s="47">
         <f t="shared" si="16"/>
-        <v>46304</v>
-      </c>
-      <c r="I38" s="50">
-        <f t="shared" si="21"/>
-        <v>15</v>
-      </c>
-      <c r="J38" s="51">
+        <v>46306</v>
+      </c>
+      <c r="I38" s="46">
+        <v>14</v>
+      </c>
+      <c r="J38" s="47">
         <f t="shared" si="17"/>
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="K38" s="37"/>
       <c r="L38" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="M38" s="49">
+      <c r="M38" s="45">
         <f t="shared" si="10"/>
-        <v>46332</v>
-      </c>
-      <c r="N38" s="50">
+        <v>46347</v>
+      </c>
+      <c r="N38" s="46">
         <v>13</v>
       </c>
-      <c r="O38" s="51">
+      <c r="O38" s="47">
         <f t="shared" si="11"/>
-        <v>46345</v>
+        <v>46360</v>
       </c>
       <c r="P38" s="34"/>
       <c r="Q38" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="R38" s="49">
+      <c r="R38" s="45">
         <f t="shared" si="12"/>
-        <v>46335</v>
-      </c>
-      <c r="S38" s="50">
-        <v>12</v>
-      </c>
-      <c r="T38" s="51">
+        <v>46351</v>
+      </c>
+      <c r="S38" s="46">
+        <v>12</v>
+      </c>
+      <c r="T38" s="47">
         <f t="shared" si="13"/>
-        <v>46347</v>
+        <v>46363</v>
       </c>
       <c r="U38" s="34"/>
-      <c r="V38" s="82" t="s">
+      <c r="V38" s="76" t="s">
         <v>44</v>
       </c>
-      <c r="W38" s="49">
+      <c r="W38" s="45">
         <f t="shared" si="6"/>
-        <v>46360</v>
-      </c>
-      <c r="X38" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y38" s="51">
+        <v>46371</v>
+      </c>
+      <c r="X38" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y38" s="47">
         <f t="shared" si="14"/>
-        <v>46371</v>
+        <v>46383</v>
       </c>
       <c r="Z38" s="34"/>
       <c r="AA38" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="AB38" s="49">
+      <c r="AB38" s="45">
         <f t="shared" si="7"/>
-        <v>46350</v>
-      </c>
-      <c r="AC38" s="50">
+        <v>46364</v>
+      </c>
+      <c r="AC38" s="46">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD38" s="51">
+        <v>12</v>
+      </c>
+      <c r="AD38" s="47">
         <f t="shared" si="15"/>
-        <v>46361</v>
+        <v>46376</v>
       </c>
     </row>
     <row r="39" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B39" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="51">
+      <c r="C39" s="47">
         <f t="shared" si="8"/>
         <v>46329</v>
       </c>
-      <c r="D39" s="50">
-        <v>13</v>
-      </c>
-      <c r="E39" s="81">
+      <c r="D39" s="46">
+        <v>12</v>
+      </c>
+      <c r="E39" s="75">
         <f t="shared" si="9"/>
-        <v>46342</v>
+        <v>46341</v>
       </c>
       <c r="F39" s="34"/>
       <c r="G39" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="H39" s="51">
+      <c r="H39" s="47">
         <f t="shared" si="16"/>
-        <v>46319</v>
-      </c>
-      <c r="I39" s="50">
-        <v>14</v>
-      </c>
-      <c r="J39" s="51">
+        <v>46320</v>
+      </c>
+      <c r="I39" s="46">
+        <v>12</v>
+      </c>
+      <c r="J39" s="47">
         <f t="shared" si="17"/>
-        <v>46333</v>
+        <v>46332</v>
       </c>
       <c r="K39" s="37"/>
       <c r="L39" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="M39" s="49">
+      <c r="M39" s="45">
         <f t="shared" si="10"/>
-        <v>46345</v>
-      </c>
-      <c r="N39" s="50">
-        <v>12</v>
-      </c>
-      <c r="O39" s="51">
+        <v>46360</v>
+      </c>
+      <c r="N39" s="46">
+        <v>12</v>
+      </c>
+      <c r="O39" s="47">
         <f t="shared" si="11"/>
-        <v>46357</v>
+        <v>46372</v>
       </c>
       <c r="P39" s="34"/>
       <c r="Q39" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="R39" s="49">
+      <c r="R39" s="45">
         <f t="shared" si="12"/>
-        <v>46347</v>
-      </c>
-      <c r="S39" s="50">
-        <v>12</v>
-      </c>
-      <c r="T39" s="51">
+        <v>46363</v>
+      </c>
+      <c r="S39" s="46">
+        <v>12</v>
+      </c>
+      <c r="T39" s="47">
         <f t="shared" si="13"/>
-        <v>46359</v>
+        <v>46375</v>
       </c>
       <c r="U39" s="34"/>
-      <c r="V39" s="82" t="s">
+      <c r="V39" s="76" t="s">
         <v>45</v>
       </c>
-      <c r="W39" s="49">
+      <c r="W39" s="45">
         <f t="shared" si="6"/>
-        <v>46371</v>
-      </c>
-      <c r="X39" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y39" s="51">
+        <v>46383</v>
+      </c>
+      <c r="X39" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y39" s="47">
         <f t="shared" si="14"/>
-        <v>46382</v>
+        <v>46395</v>
       </c>
       <c r="Z39" s="34"/>
       <c r="AA39" s="35" t="s">
         <v>45</v>
       </c>
-      <c r="AB39" s="49">
+      <c r="AB39" s="45">
         <f t="shared" si="7"/>
-        <v>46361</v>
-      </c>
-      <c r="AC39" s="50">
+        <v>46376</v>
+      </c>
+      <c r="AC39" s="46">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD39" s="51">
+        <v>12</v>
+      </c>
+      <c r="AD39" s="47">
         <f t="shared" si="15"/>
-        <v>46372</v>
+        <v>46388</v>
       </c>
     </row>
     <row r="40" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B40" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="51">
+      <c r="C40" s="47">
         <f t="shared" si="8"/>
-        <v>46342</v>
-      </c>
-      <c r="D40" s="50">
-        <v>12</v>
-      </c>
-      <c r="E40" s="81">
+        <v>46341</v>
+      </c>
+      <c r="D40" s="46">
+        <v>12</v>
+      </c>
+      <c r="E40" s="75">
         <f t="shared" si="9"/>
-        <v>46354</v>
+        <v>46353</v>
       </c>
       <c r="F40" s="34"/>
       <c r="G40" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="H40" s="51">
+      <c r="H40" s="47">
         <f t="shared" si="16"/>
-        <v>46333</v>
-      </c>
-      <c r="I40" s="50">
+        <v>46332</v>
+      </c>
+      <c r="I40" s="46">
         <v>13</v>
       </c>
-      <c r="J40" s="51">
+      <c r="J40" s="47">
         <f t="shared" si="17"/>
-        <v>46346</v>
+        <v>46345</v>
       </c>
       <c r="K40" s="37"/>
       <c r="L40" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="M40" s="49">
+      <c r="M40" s="45">
         <f t="shared" si="10"/>
-        <v>46357</v>
-      </c>
-      <c r="N40" s="50">
-        <v>12</v>
-      </c>
-      <c r="O40" s="51">
+        <v>46372</v>
+      </c>
+      <c r="N40" s="46">
+        <v>12</v>
+      </c>
+      <c r="O40" s="47">
         <f t="shared" si="11"/>
-        <v>46369</v>
+        <v>46384</v>
       </c>
       <c r="P40" s="34"/>
       <c r="Q40" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="R40" s="49">
+      <c r="R40" s="45">
         <f t="shared" si="12"/>
-        <v>46359</v>
-      </c>
-      <c r="S40" s="50">
-        <v>12</v>
-      </c>
-      <c r="T40" s="51">
+        <v>46375</v>
+      </c>
+      <c r="S40" s="46">
+        <v>12</v>
+      </c>
+      <c r="T40" s="47">
         <f t="shared" si="13"/>
-        <v>46371</v>
+        <v>46387</v>
       </c>
       <c r="U40" s="34"/>
-      <c r="V40" s="82" t="s">
+      <c r="V40" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="W40" s="49">
+      <c r="W40" s="45">
         <f t="shared" si="6"/>
-        <v>46382</v>
-      </c>
-      <c r="X40" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y40" s="51">
+        <v>46395</v>
+      </c>
+      <c r="X40" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y40" s="47">
         <f t="shared" si="14"/>
-        <v>46393</v>
+        <v>46407</v>
       </c>
       <c r="Z40" s="34"/>
       <c r="AA40" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="AB40" s="49">
+      <c r="AB40" s="45">
         <f t="shared" si="7"/>
-        <v>46372</v>
-      </c>
-      <c r="AC40" s="50">
+        <v>46388</v>
+      </c>
+      <c r="AC40" s="46">
         <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD40" s="51">
+        <v>12</v>
+      </c>
+      <c r="AD40" s="47">
         <f t="shared" si="15"/>
-        <v>46383</v>
+        <v>46400</v>
       </c>
     </row>
     <row r="41" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B41" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="C41" s="51">
+      <c r="C41" s="47">
         <f t="shared" si="8"/>
-        <v>46354</v>
-      </c>
-      <c r="D41" s="50">
-        <v>12</v>
-      </c>
-      <c r="E41" s="81">
+        <v>46353</v>
+      </c>
+      <c r="D41" s="46">
+        <v>12</v>
+      </c>
+      <c r="E41" s="75">
         <f t="shared" si="9"/>
-        <v>46366</v>
+        <v>46365</v>
       </c>
       <c r="F41" s="34"/>
       <c r="G41" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="H41" s="51">
+      <c r="H41" s="47">
         <f t="shared" si="16"/>
-        <v>46346</v>
-      </c>
-      <c r="I41" s="50">
+        <v>46345</v>
+      </c>
+      <c r="I41" s="46">
         <v>13</v>
       </c>
-      <c r="J41" s="51">
+      <c r="J41" s="47">
         <f t="shared" si="17"/>
-        <v>46359</v>
+        <v>46358</v>
       </c>
       <c r="K41" s="37"/>
       <c r="L41" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="M41" s="49">
+      <c r="M41" s="45">
         <f t="shared" si="10"/>
-        <v>46369</v>
-      </c>
-      <c r="N41" s="50">
-        <v>12</v>
-      </c>
-      <c r="O41" s="51">
+        <v>46384</v>
+      </c>
+      <c r="N41" s="46">
+        <v>12</v>
+      </c>
+      <c r="O41" s="47">
         <f t="shared" si="11"/>
-        <v>46381</v>
+        <v>46396</v>
       </c>
       <c r="P41" s="34"/>
       <c r="Q41" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="R41" s="49">
+      <c r="R41" s="45">
         <f t="shared" si="12"/>
-        <v>46371</v>
-      </c>
-      <c r="S41" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T41" s="51">
+        <v>46387</v>
+      </c>
+      <c r="S41" s="46">
+        <v>11</v>
+      </c>
+      <c r="T41" s="47">
         <f t="shared" si="13"/>
-        <v>46383</v>
+        <v>46398</v>
       </c>
       <c r="U41" s="34"/>
-      <c r="V41" s="82" t="s">
+      <c r="V41" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="W41" s="49">
+      <c r="W41" s="45">
         <f t="shared" si="6"/>
-        <v>46393</v>
-      </c>
-      <c r="X41" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y41" s="51">
+        <v>46407</v>
+      </c>
+      <c r="X41" s="46">
+        <v>12</v>
+      </c>
+      <c r="Y41" s="47">
         <f t="shared" si="14"/>
-        <v>46404</v>
+        <v>46419</v>
       </c>
       <c r="Z41" s="34"/>
       <c r="AA41" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="AB41" s="49">
+      <c r="AB41" s="45">
         <f t="shared" si="7"/>
-        <v>46383</v>
-      </c>
-      <c r="AC41" s="50">
-        <f t="shared" si="18"/>
+        <v>46400</v>
+      </c>
+      <c r="AC41" s="46">
         <v>11</v>
       </c>
-      <c r="AD41" s="51">
+      <c r="AD41" s="47">
         <f t="shared" si="15"/>
-        <v>46394</v>
+        <v>46411</v>
       </c>
     </row>
     <row r="42" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B42" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="C42" s="51">
+      <c r="C42" s="47">
         <f t="shared" si="8"/>
-        <v>46366</v>
-      </c>
-      <c r="D42" s="50">
-        <v>12</v>
-      </c>
-      <c r="E42" s="81">
+        <v>46365</v>
+      </c>
+      <c r="D42" s="46">
+        <v>12</v>
+      </c>
+      <c r="E42" s="75">
         <f t="shared" si="9"/>
-        <v>46378</v>
+        <v>46377</v>
       </c>
       <c r="F42" s="34"/>
       <c r="G42" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="H42" s="51">
+      <c r="H42" s="47">
         <f t="shared" si="16"/>
-        <v>46359</v>
-      </c>
-      <c r="I42" s="50">
+        <v>46358</v>
+      </c>
+      <c r="I42" s="46">
         <v>13</v>
       </c>
-      <c r="J42" s="51">
+      <c r="J42" s="47">
         <f t="shared" si="17"/>
-        <v>46372</v>
+        <v>46371</v>
       </c>
       <c r="K42" s="37"/>
       <c r="L42" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="M42" s="49">
+      <c r="M42" s="45">
         <f t="shared" si="10"/>
-        <v>46381</v>
-      </c>
-      <c r="N42" s="50">
-        <v>12</v>
-      </c>
-      <c r="O42" s="51">
+        <v>46396</v>
+      </c>
+      <c r="N42" s="46">
+        <v>12</v>
+      </c>
+      <c r="O42" s="47">
         <f t="shared" si="11"/>
-        <v>46393</v>
+        <v>46408</v>
       </c>
       <c r="P42" s="34"/>
       <c r="Q42" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="R42" s="49">
+      <c r="R42" s="45">
         <f t="shared" si="12"/>
-        <v>46383</v>
-      </c>
-      <c r="S42" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T42" s="51">
+        <v>46398</v>
+      </c>
+      <c r="S42" s="46">
+        <v>11</v>
+      </c>
+      <c r="T42" s="47">
         <f t="shared" si="13"/>
-        <v>46395</v>
+        <v>46409</v>
       </c>
       <c r="U42" s="34"/>
-      <c r="V42" s="82" t="s">
+      <c r="V42" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="W42" s="49">
+      <c r="W42" s="45">
         <f t="shared" si="6"/>
-        <v>46404</v>
-      </c>
-      <c r="X42" s="50">
+        <v>46419</v>
+      </c>
+      <c r="X42" s="46">
         <v>11</v>
       </c>
-      <c r="Y42" s="51">
+      <c r="Y42" s="47">
         <f t="shared" si="14"/>
-        <v>46415</v>
+        <v>46430</v>
       </c>
       <c r="Z42" s="34"/>
       <c r="AA42" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="AB42" s="49">
+      <c r="AB42" s="45">
         <f t="shared" si="7"/>
-        <v>46394</v>
-      </c>
-      <c r="AC42" s="50">
-        <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD42" s="51">
+        <v>46411</v>
+      </c>
+      <c r="AC42" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD42" s="47">
         <f t="shared" si="15"/>
-        <v>46405</v>
+        <v>46423</v>
       </c>
     </row>
     <row r="43" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B43" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="C43" s="51">
+      <c r="C43" s="47">
         <f t="shared" si="8"/>
-        <v>46378</v>
-      </c>
-      <c r="D43" s="50">
-        <v>12</v>
-      </c>
-      <c r="E43" s="81">
+        <v>46377</v>
+      </c>
+      <c r="D43" s="46">
+        <v>12</v>
+      </c>
+      <c r="E43" s="75">
         <f t="shared" si="9"/>
-        <v>46390</v>
+        <v>46389</v>
       </c>
       <c r="F43" s="34"/>
       <c r="G43" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="H43" s="51">
+      <c r="H43" s="47">
         <f t="shared" si="16"/>
-        <v>46372</v>
-      </c>
-      <c r="I43" s="50">
+        <v>46371</v>
+      </c>
+      <c r="I43" s="46">
         <v>13</v>
       </c>
-      <c r="J43" s="51">
+      <c r="J43" s="47">
         <f t="shared" si="17"/>
-        <v>46385</v>
+        <v>46384</v>
       </c>
       <c r="K43" s="37"/>
       <c r="L43" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="M43" s="49">
+      <c r="M43" s="45">
         <f t="shared" si="10"/>
-        <v>46393</v>
-      </c>
-      <c r="N43" s="50">
-        <v>12</v>
-      </c>
-      <c r="O43" s="51">
+        <v>46408</v>
+      </c>
+      <c r="N43" s="46">
+        <v>12</v>
+      </c>
+      <c r="O43" s="47">
         <f t="shared" si="11"/>
-        <v>46405</v>
+        <v>46420</v>
       </c>
       <c r="P43" s="34"/>
       <c r="Q43" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="R43" s="49">
+      <c r="R43" s="45">
         <f t="shared" si="12"/>
-        <v>46395</v>
-      </c>
-      <c r="S43" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T43" s="51">
+        <v>46409</v>
+      </c>
+      <c r="S43" s="46">
+        <v>11</v>
+      </c>
+      <c r="T43" s="47">
         <f t="shared" si="13"/>
-        <v>46407</v>
+        <v>46420</v>
       </c>
       <c r="U43" s="34"/>
-      <c r="V43" s="82" t="s">
+      <c r="V43" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="W43" s="49">
+      <c r="W43" s="45">
         <f t="shared" si="6"/>
-        <v>46415</v>
-      </c>
-      <c r="X43" s="50">
+        <v>46430</v>
+      </c>
+      <c r="X43" s="46">
         <v>11</v>
       </c>
-      <c r="Y43" s="51">
+      <c r="Y43" s="47">
         <f t="shared" si="14"/>
-        <v>46426</v>
+        <v>46441</v>
       </c>
       <c r="Z43" s="34"/>
       <c r="AA43" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="AB43" s="49">
+      <c r="AB43" s="45">
         <f t="shared" si="7"/>
-        <v>46405</v>
-      </c>
-      <c r="AC43" s="50">
-        <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD43" s="51">
+        <v>46423</v>
+      </c>
+      <c r="AC43" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD43" s="47">
         <f t="shared" si="15"/>
-        <v>46416</v>
+        <v>46435</v>
       </c>
     </row>
     <row r="44" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B44" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="C44" s="51">
+      <c r="C44" s="47">
         <f t="shared" si="8"/>
-        <v>46390</v>
-      </c>
-      <c r="D44" s="50">
-        <v>12</v>
-      </c>
-      <c r="E44" s="81">
+        <v>46389</v>
+      </c>
+      <c r="D44" s="46">
+        <v>12</v>
+      </c>
+      <c r="E44" s="75">
         <f t="shared" si="9"/>
-        <v>46402</v>
+        <v>46401</v>
       </c>
       <c r="F44" s="34"/>
       <c r="G44" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="H44" s="51">
+      <c r="H44" s="47">
         <f t="shared" si="16"/>
-        <v>46385</v>
-      </c>
-      <c r="I44" s="50">
+        <v>46384</v>
+      </c>
+      <c r="I44" s="46">
         <v>13</v>
       </c>
-      <c r="J44" s="51">
+      <c r="J44" s="47">
         <f t="shared" si="17"/>
-        <v>46398</v>
+        <v>46397</v>
       </c>
       <c r="K44" s="37"/>
       <c r="L44" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="M44" s="49">
+      <c r="M44" s="45">
         <f t="shared" si="10"/>
-        <v>46405</v>
-      </c>
-      <c r="N44" s="50">
-        <v>12</v>
-      </c>
-      <c r="O44" s="51">
+        <v>46420</v>
+      </c>
+      <c r="N44" s="46">
+        <v>12</v>
+      </c>
+      <c r="O44" s="47">
         <f t="shared" si="11"/>
-        <v>46417</v>
+        <v>46432</v>
       </c>
       <c r="P44" s="34"/>
       <c r="Q44" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="R44" s="49">
+      <c r="R44" s="45">
         <f t="shared" si="12"/>
-        <v>46407</v>
-      </c>
-      <c r="S44" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T44" s="51">
+        <v>46420</v>
+      </c>
+      <c r="S44" s="46">
+        <f t="shared" ref="S44:S49" si="21">N44</f>
+        <v>12</v>
+      </c>
+      <c r="T44" s="47">
         <f t="shared" si="13"/>
-        <v>46419</v>
+        <v>46432</v>
       </c>
       <c r="U44" s="34"/>
-      <c r="V44" s="82" t="s">
+      <c r="V44" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="W44" s="49">
+      <c r="W44" s="45">
         <f t="shared" si="6"/>
-        <v>46426</v>
-      </c>
-      <c r="X44" s="50">
+        <v>46441</v>
+      </c>
+      <c r="X44" s="46">
         <v>11</v>
       </c>
-      <c r="Y44" s="51">
+      <c r="Y44" s="47">
         <f t="shared" si="14"/>
-        <v>46437</v>
+        <v>46452</v>
       </c>
       <c r="Z44" s="34"/>
       <c r="AA44" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="AB44" s="49">
+      <c r="AB44" s="45">
         <f t="shared" si="7"/>
-        <v>46416</v>
-      </c>
-      <c r="AC44" s="50">
-        <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD44" s="51">
+        <v>46435</v>
+      </c>
+      <c r="AC44" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD44" s="47">
         <f t="shared" si="15"/>
-        <v>46427</v>
+        <v>46447</v>
       </c>
     </row>
     <row r="45" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B45" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="51">
+      <c r="C45" s="47">
         <f t="shared" si="8"/>
-        <v>46402</v>
-      </c>
-      <c r="D45" s="50">
-        <v>12</v>
-      </c>
-      <c r="E45" s="81">
+        <v>46401</v>
+      </c>
+      <c r="D45" s="46">
+        <v>12</v>
+      </c>
+      <c r="E45" s="75">
         <f t="shared" si="9"/>
-        <v>46414</v>
+        <v>46413</v>
       </c>
       <c r="F45" s="34"/>
       <c r="G45" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="H45" s="51">
+      <c r="H45" s="47">
         <f t="shared" si="16"/>
-        <v>46398</v>
-      </c>
-      <c r="I45" s="50">
+        <v>46397</v>
+      </c>
+      <c r="I45" s="46">
         <v>13</v>
       </c>
-      <c r="J45" s="51">
+      <c r="J45" s="47">
         <f t="shared" si="17"/>
-        <v>46411</v>
+        <v>46410</v>
       </c>
       <c r="K45" s="37"/>
       <c r="L45" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="M45" s="49">
+      <c r="M45" s="45">
         <f t="shared" si="10"/>
-        <v>46417</v>
-      </c>
-      <c r="N45" s="50">
-        <v>12</v>
-      </c>
-      <c r="O45" s="51">
+        <v>46432</v>
+      </c>
+      <c r="N45" s="46">
+        <v>12</v>
+      </c>
+      <c r="O45" s="47">
         <f t="shared" si="11"/>
-        <v>46429</v>
+        <v>46444</v>
       </c>
       <c r="P45" s="34"/>
       <c r="Q45" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="R45" s="49">
+      <c r="R45" s="45">
         <f t="shared" si="12"/>
-        <v>46419</v>
-      </c>
-      <c r="S45" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T45" s="51">
+        <v>46432</v>
+      </c>
+      <c r="S45" s="46">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="T45" s="47">
         <f t="shared" si="13"/>
-        <v>46431</v>
+        <v>46444</v>
       </c>
       <c r="U45" s="34"/>
-      <c r="V45" s="82" t="s">
+      <c r="V45" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="W45" s="49">
+      <c r="W45" s="45">
         <f t="shared" si="6"/>
-        <v>46437</v>
-      </c>
-      <c r="X45" s="50">
+        <v>46452</v>
+      </c>
+      <c r="X45" s="46">
         <v>11</v>
       </c>
-      <c r="Y45" s="51">
+      <c r="Y45" s="47">
         <f t="shared" si="14"/>
-        <v>46448</v>
+        <v>46463</v>
       </c>
       <c r="Z45" s="34"/>
       <c r="AA45" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="AB45" s="49">
+      <c r="AB45" s="45">
         <f t="shared" si="7"/>
-        <v>46427</v>
-      </c>
-      <c r="AC45" s="50">
-        <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD45" s="51">
+        <v>46447</v>
+      </c>
+      <c r="AC45" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD45" s="47">
         <f t="shared" si="15"/>
-        <v>46438</v>
+        <v>46459</v>
       </c>
     </row>
     <row r="46" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B46" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="C46" s="51">
+      <c r="C46" s="47">
         <f t="shared" si="8"/>
-        <v>46414</v>
-      </c>
-      <c r="D46" s="50">
-        <v>12</v>
-      </c>
-      <c r="E46" s="81">
+        <v>46413</v>
+      </c>
+      <c r="D46" s="46">
+        <v>12</v>
+      </c>
+      <c r="E46" s="75">
         <f t="shared" si="9"/>
-        <v>46426</v>
+        <v>46425</v>
       </c>
       <c r="F46" s="34"/>
       <c r="G46" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="H46" s="51">
+      <c r="H46" s="47">
         <f t="shared" si="16"/>
-        <v>46411</v>
-      </c>
-      <c r="I46" s="50">
+        <v>46410</v>
+      </c>
+      <c r="I46" s="46">
         <v>13</v>
       </c>
-      <c r="J46" s="51">
+      <c r="J46" s="47">
         <f t="shared" si="17"/>
-        <v>46424</v>
+        <v>46423</v>
       </c>
       <c r="K46" s="37"/>
       <c r="L46" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="M46" s="49">
+      <c r="M46" s="45">
         <f t="shared" si="10"/>
-        <v>46429</v>
-      </c>
-      <c r="N46" s="50">
-        <v>12</v>
-      </c>
-      <c r="O46" s="51">
+        <v>46444</v>
+      </c>
+      <c r="N46" s="46">
+        <v>12</v>
+      </c>
+      <c r="O46" s="47">
         <f t="shared" si="11"/>
-        <v>46441</v>
+        <v>46456</v>
       </c>
       <c r="P46" s="34"/>
       <c r="Q46" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="R46" s="49">
+      <c r="R46" s="45">
         <f t="shared" si="12"/>
-        <v>46431</v>
-      </c>
-      <c r="S46" s="50">
-        <f t="shared" si="19"/>
-        <v>12</v>
-      </c>
-      <c r="T46" s="51">
+        <v>46444</v>
+      </c>
+      <c r="S46" s="46">
+        <f t="shared" si="21"/>
+        <v>12</v>
+      </c>
+      <c r="T46" s="47">
         <f t="shared" si="13"/>
-        <v>46443</v>
+        <v>46456</v>
       </c>
       <c r="U46" s="34"/>
-      <c r="V46" s="82" t="s">
+      <c r="V46" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="W46" s="49">
+      <c r="W46" s="45">
         <f t="shared" si="6"/>
-        <v>46448</v>
-      </c>
-      <c r="X46" s="50">
+        <v>46463</v>
+      </c>
+      <c r="X46" s="46">
         <v>11</v>
       </c>
-      <c r="Y46" s="51">
+      <c r="Y46" s="47">
         <f t="shared" si="14"/>
-        <v>46459</v>
+        <v>46474</v>
       </c>
       <c r="Z46" s="34"/>
       <c r="AA46" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="AB46" s="49">
+      <c r="AB46" s="45">
         <f t="shared" si="7"/>
-        <v>46438</v>
-      </c>
-      <c r="AC46" s="50">
-        <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD46" s="51">
+        <v>46459</v>
+      </c>
+      <c r="AC46" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD46" s="47">
         <f t="shared" si="15"/>
-        <v>46449</v>
+        <v>46471</v>
       </c>
     </row>
     <row r="47" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B47" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C47" s="51">
+      <c r="C47" s="47">
         <f t="shared" si="8"/>
-        <v>46426</v>
-      </c>
-      <c r="D47" s="50">
-        <v>14</v>
-      </c>
-      <c r="E47" s="81">
+        <v>46425</v>
+      </c>
+      <c r="D47" s="46">
+        <v>13</v>
+      </c>
+      <c r="E47" s="75">
         <f t="shared" si="9"/>
-        <v>46440</v>
+        <v>46438</v>
       </c>
       <c r="F47" s="34"/>
       <c r="G47" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="H47" s="51">
+      <c r="H47" s="47">
         <f t="shared" si="16"/>
-        <v>46424</v>
-      </c>
-      <c r="I47" s="50">
+        <v>46423</v>
+      </c>
+      <c r="I47" s="46">
         <v>15</v>
       </c>
-      <c r="J47" s="51">
+      <c r="J47" s="47">
         <f t="shared" si="17"/>
-        <v>46439</v>
+        <v>46438</v>
       </c>
       <c r="K47" s="37"/>
       <c r="L47" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="M47" s="49">
+      <c r="M47" s="45">
         <f t="shared" si="10"/>
-        <v>46441</v>
-      </c>
-      <c r="N47" s="50">
-        <v>12</v>
-      </c>
-      <c r="O47" s="51">
+        <v>46456</v>
+      </c>
+      <c r="N47" s="46">
+        <v>12</v>
+      </c>
+      <c r="O47" s="47">
         <f t="shared" si="11"/>
-        <v>46453</v>
+        <v>46468</v>
       </c>
       <c r="P47" s="34"/>
       <c r="Q47" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="R47" s="49">
+      <c r="R47" s="45">
         <f t="shared" si="12"/>
-        <v>46443</v>
-      </c>
-      <c r="S47" s="50">
+        <v>46456</v>
+      </c>
+      <c r="S47" s="46">
+        <v>12</v>
+      </c>
+      <c r="T47" s="47">
+        <f t="shared" si="13"/>
+        <v>46468</v>
+      </c>
+      <c r="U47" s="34"/>
+      <c r="V47" s="76" t="s">
+        <v>53</v>
+      </c>
+      <c r="W47" s="45">
+        <f t="shared" si="6"/>
+        <v>46474</v>
+      </c>
+      <c r="X47" s="46">
         <v>11</v>
       </c>
-      <c r="T47" s="51">
-        <f t="shared" si="13"/>
-        <v>46454</v>
-      </c>
-      <c r="U47" s="34"/>
-      <c r="V47" s="82" t="s">
-        <v>53</v>
-      </c>
-      <c r="W47" s="49">
-        <f t="shared" si="6"/>
-        <v>46459</v>
-      </c>
-      <c r="X47" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y47" s="51">
+      <c r="Y47" s="47">
         <f t="shared" si="14"/>
-        <v>46470</v>
+        <v>46485</v>
       </c>
       <c r="Z47" s="34"/>
       <c r="AA47" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="AB47" s="49">
+      <c r="AB47" s="45">
         <f t="shared" si="7"/>
-        <v>46449</v>
-      </c>
-      <c r="AC47" s="50">
-        <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD47" s="51">
+        <v>46471</v>
+      </c>
+      <c r="AC47" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD47" s="47">
         <f t="shared" si="15"/>
-        <v>46460</v>
+        <v>46483</v>
       </c>
     </row>
     <row r="48" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B48" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="51">
+      <c r="C48" s="47">
         <f t="shared" si="8"/>
-        <v>46440</v>
-      </c>
-      <c r="D48" s="50">
-        <v>12</v>
-      </c>
-      <c r="E48" s="81">
+        <v>46438</v>
+      </c>
+      <c r="D48" s="46">
+        <v>13</v>
+      </c>
+      <c r="E48" s="75">
         <f t="shared" si="9"/>
-        <v>46452</v>
+        <v>46451</v>
       </c>
       <c r="F48" s="34"/>
       <c r="G48" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="H48" s="51">
+      <c r="H48" s="47">
         <f t="shared" si="16"/>
-        <v>46439</v>
-      </c>
-      <c r="I48" s="50">
+        <v>46438</v>
+      </c>
+      <c r="I48" s="46">
         <v>13</v>
       </c>
-      <c r="J48" s="51">
+      <c r="J48" s="47">
         <f t="shared" si="17"/>
-        <v>46452</v>
+        <v>46451</v>
       </c>
       <c r="K48" s="37"/>
       <c r="L48" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="M48" s="49">
+      <c r="M48" s="45">
         <f t="shared" si="10"/>
-        <v>46453</v>
-      </c>
-      <c r="N48" s="50">
-        <v>12</v>
-      </c>
-      <c r="O48" s="51">
+        <v>46468</v>
+      </c>
+      <c r="N48" s="46">
+        <v>12</v>
+      </c>
+      <c r="O48" s="47">
         <f t="shared" si="11"/>
-        <v>46465</v>
+        <v>46480</v>
       </c>
       <c r="P48" s="34"/>
       <c r="Q48" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="R48" s="49">
+      <c r="R48" s="45">
         <f t="shared" si="12"/>
-        <v>46454</v>
-      </c>
-      <c r="S48" s="50">
+        <v>46468</v>
+      </c>
+      <c r="S48" s="46">
+        <v>12</v>
+      </c>
+      <c r="T48" s="47">
+        <f t="shared" si="13"/>
+        <v>46480</v>
+      </c>
+      <c r="U48" s="34"/>
+      <c r="V48" s="76" t="s">
+        <v>54</v>
+      </c>
+      <c r="W48" s="45">
+        <f t="shared" si="6"/>
+        <v>46485</v>
+      </c>
+      <c r="X48" s="46">
         <v>11</v>
       </c>
-      <c r="T48" s="51">
-        <f t="shared" si="13"/>
-        <v>46465</v>
-      </c>
-      <c r="U48" s="34"/>
-      <c r="V48" s="82" t="s">
-        <v>54</v>
-      </c>
-      <c r="W48" s="49">
-        <f t="shared" si="6"/>
-        <v>46470</v>
-      </c>
-      <c r="X48" s="50">
-        <v>11</v>
-      </c>
-      <c r="Y48" s="51">
+      <c r="Y48" s="47">
         <f t="shared" si="14"/>
-        <v>46481</v>
+        <v>46496</v>
       </c>
       <c r="Z48" s="34"/>
       <c r="AA48" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="AB48" s="49">
+      <c r="AB48" s="45">
         <f t="shared" si="7"/>
-        <v>46460</v>
-      </c>
-      <c r="AC48" s="50">
-        <f t="shared" si="18"/>
-        <v>11</v>
-      </c>
-      <c r="AD48" s="51">
+        <v>46483</v>
+      </c>
+      <c r="AC48" s="46">
+        <v>12</v>
+      </c>
+      <c r="AD48" s="47">
         <f t="shared" si="15"/>
-        <v>46471</v>
+        <v>46495</v>
       </c>
     </row>
     <row r="49" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
       <c r="B49" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="C49" s="51">
+      <c r="C49" s="47">
         <f t="shared" si="8"/>
-        <v>46452</v>
-      </c>
-      <c r="D49" s="50">
-        <v>12</v>
-      </c>
-      <c r="E49" s="81">
+        <v>46451</v>
+      </c>
+      <c r="D49" s="46">
+        <v>13</v>
+      </c>
+      <c r="E49" s="75">
         <f t="shared" si="9"/>
         <v>46464</v>
       </c>
@@ -6860,82 +6863,82 @@
       <c r="G49" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="H49" s="51">
+      <c r="H49" s="47">
         <f t="shared" si="16"/>
-        <v>46452</v>
-      </c>
-      <c r="I49" s="50">
-        <f t="shared" si="21"/>
-        <v>12</v>
-      </c>
-      <c r="J49" s="51">
+        <v>46451</v>
+      </c>
+      <c r="I49" s="46">
+        <f t="shared" si="20"/>
+        <v>13</v>
+      </c>
+      <c r="J49" s="47">
         <f t="shared" si="17"/>
         <v>46464</v>
       </c>
       <c r="K49" s="37"/>
-      <c r="L49" s="54" t="s">
+      <c r="L49" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="M49" s="85">
+      <c r="M49" s="79">
         <f t="shared" si="10"/>
-        <v>46465</v>
+        <v>46480</v>
       </c>
       <c r="N49" s="32">
         <v>12</v>
       </c>
       <c r="O49" s="31">
         <f t="shared" si="11"/>
-        <v>46477</v>
+        <v>46492</v>
       </c>
       <c r="P49" s="34"/>
-      <c r="Q49" s="54" t="s">
+      <c r="Q49" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="R49" s="85">
+      <c r="R49" s="79">
         <f t="shared" si="12"/>
-        <v>46465</v>
+        <v>46480</v>
       </c>
       <c r="S49" s="32">
-        <f t="shared" si="19"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="T49" s="31">
         <f t="shared" si="13"/>
-        <v>46477</v>
+        <v>46492</v>
       </c>
       <c r="U49" s="34"/>
-      <c r="V49" s="86" t="s">
+      <c r="V49" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="W49" s="85">
+      <c r="W49" s="79">
         <f t="shared" si="6"/>
-        <v>46481</v>
+        <v>46496</v>
       </c>
       <c r="X49" s="32">
         <v>11</v>
       </c>
       <c r="Y49" s="31">
         <f t="shared" si="14"/>
-        <v>46492</v>
+        <v>46507</v>
       </c>
       <c r="Z49" s="34"/>
-      <c r="AA49" s="54" t="s">
+      <c r="AA49" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="AB49" s="85">
+      <c r="AB49" s="79">
         <f t="shared" si="7"/>
-        <v>46471</v>
+        <v>46495</v>
       </c>
       <c r="AC49" s="32">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD49" s="31">
         <f t="shared" si="15"/>
-        <v>46484</v>
+        <v>46507</v>
       </c>
     </row>
     <row r="50" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
-      <c r="B50" s="54" t="s">
+      <c r="B50" s="50" t="s">
         <v>56</v>
       </c>
       <c r="C50" s="31">
@@ -6950,7 +6953,7 @@
         <v>46477</v>
       </c>
       <c r="F50" s="34"/>
-      <c r="G50" s="54" t="s">
+      <c r="G50" s="50" t="s">
         <v>56</v>
       </c>
       <c r="H50" s="31">
@@ -6958,7 +6961,7 @@
         <v>46464</v>
       </c>
       <c r="I50" s="32">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>13</v>
       </c>
       <c r="J50" s="31">
@@ -6969,75 +6972,75 @@
       <c r="L50" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="M50" s="49">
+      <c r="M50" s="45">
         <f t="shared" si="10"/>
-        <v>46477</v>
-      </c>
-      <c r="N50" s="50">
+        <v>46492</v>
+      </c>
+      <c r="N50" s="46">
         <v>14</v>
       </c>
-      <c r="O50" s="51">
+      <c r="O50" s="47">
         <f t="shared" si="11"/>
-        <v>46491</v>
+        <v>46506</v>
       </c>
       <c r="P50" s="34"/>
       <c r="Q50" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="R50" s="49">
+      <c r="R50" s="45">
         <f t="shared" si="12"/>
-        <v>46477</v>
-      </c>
-      <c r="S50" s="50">
+        <v>46492</v>
+      </c>
+      <c r="S50" s="46">
         <v>14</v>
       </c>
-      <c r="T50" s="51">
+      <c r="T50" s="47">
         <f t="shared" si="13"/>
-        <v>46491</v>
+        <v>46506</v>
       </c>
       <c r="U50" s="34"/>
-      <c r="V50" s="82" t="s">
+      <c r="V50" s="76" t="s">
         <v>56</v>
       </c>
-      <c r="W50" s="49">
+      <c r="W50" s="45">
         <f t="shared" si="6"/>
-        <v>46492</v>
-      </c>
-      <c r="X50" s="50">
+        <v>46507</v>
+      </c>
+      <c r="X50" s="46">
         <v>24</v>
       </c>
-      <c r="Y50" s="51">
+      <c r="Y50" s="47">
         <f t="shared" si="14"/>
-        <v>46516</v>
+        <v>46531</v>
       </c>
       <c r="Z50" s="34"/>
       <c r="AA50" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="AB50" s="49">
+      <c r="AB50" s="45">
         <f t="shared" si="7"/>
-        <v>46484</v>
-      </c>
-      <c r="AC50" s="50">
+        <v>46507</v>
+      </c>
+      <c r="AC50" s="46">
         <v>24</v>
       </c>
-      <c r="AD50" s="51">
+      <c r="AD50" s="47">
         <f t="shared" si="15"/>
-        <v>46508</v>
+        <v>46531</v>
       </c>
     </row>
     <row r="51" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B51" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="51">
+      <c r="C51" s="47">
         <f t="shared" si="8"/>
         <v>46477</v>
       </c>
-      <c r="D51" s="50">
+      <c r="D51" s="46">
         <v>14</v>
       </c>
-      <c r="E51" s="81">
+      <c r="E51" s="75">
         <f t="shared" si="9"/>
         <v>46491</v>
       </c>
@@ -7045,14 +7048,14 @@
       <c r="G51" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="H51" s="51">
+      <c r="H51" s="47">
         <f t="shared" si="16"/>
         <v>46477</v>
       </c>
-      <c r="I51" s="50">
+      <c r="I51" s="46">
         <v>14</v>
       </c>
-      <c r="J51" s="51">
+      <c r="J51" s="47">
         <f t="shared" si="17"/>
         <v>46491</v>
       </c>
@@ -7060,75 +7063,75 @@
       <c r="L51" s="35" t="s">
         <v>57</v>
       </c>
-      <c r="M51" s="49">
+      <c r="M51" s="45">
         <f t="shared" si="10"/>
-        <v>46491</v>
-      </c>
-      <c r="N51" s="50">
+        <v>46506</v>
+      </c>
+      <c r="N51" s="46">
         <v>24</v>
       </c>
-      <c r="O51" s="51">
+      <c r="O51" s="47">
         <f t="shared" si="11"/>
-        <v>46515</v>
+        <v>46530</v>
       </c>
       <c r="P51" s="34"/>
       <c r="Q51" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="R51" s="58">
+      <c r="R51" s="54">
         <f t="shared" si="12"/>
-        <v>46491</v>
-      </c>
-      <c r="S51" s="50">
+        <v>46506</v>
+      </c>
+      <c r="S51" s="46">
         <v>24</v>
       </c>
-      <c r="T51" s="55">
+      <c r="T51" s="51">
         <f t="shared" si="13"/>
-        <v>46515</v>
+        <v>46530</v>
       </c>
       <c r="U51" s="34"/>
-      <c r="V51" s="83" t="s">
+      <c r="V51" s="77" t="s">
         <v>57</v>
       </c>
-      <c r="W51" s="58">
+      <c r="W51" s="54">
         <f t="shared" si="6"/>
-        <v>46516</v>
-      </c>
-      <c r="X51" s="50">
+        <v>46531</v>
+      </c>
+      <c r="X51" s="46">
         <v>26</v>
       </c>
-      <c r="Y51" s="55">
+      <c r="Y51" s="51">
         <f t="shared" si="14"/>
-        <v>46542</v>
+        <v>46557</v>
       </c>
       <c r="Z51" s="34"/>
       <c r="AA51" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="AB51" s="58">
+      <c r="AB51" s="54">
         <f t="shared" si="7"/>
-        <v>46508</v>
-      </c>
-      <c r="AC51" s="50">
+        <v>46531</v>
+      </c>
+      <c r="AC51" s="46">
         <v>26</v>
       </c>
-      <c r="AD51" s="55">
+      <c r="AD51" s="51">
         <f t="shared" si="15"/>
-        <v>46534</v>
+        <v>46557</v>
       </c>
     </row>
     <row r="52" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B52" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="55">
+      <c r="C52" s="51">
         <f t="shared" si="8"/>
         <v>46491</v>
       </c>
-      <c r="D52" s="56">
+      <c r="D52" s="52">
         <v>24</v>
       </c>
-      <c r="E52" s="57">
+      <c r="E52" s="53">
         <f t="shared" si="9"/>
         <v>46515</v>
       </c>
@@ -7136,550 +7139,550 @@
       <c r="G52" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="H52" s="55">
+      <c r="H52" s="51">
         <f t="shared" si="16"/>
         <v>46491</v>
       </c>
-      <c r="I52" s="56">
+      <c r="I52" s="52">
         <v>24</v>
       </c>
-      <c r="J52" s="55">
+      <c r="J52" s="51">
         <f t="shared" si="17"/>
         <v>46515</v>
       </c>
       <c r="K52" s="37"/>
-      <c r="L52" s="61" t="s">
+      <c r="L52" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="M52" s="69">
+      <c r="M52" s="63">
         <f t="shared" si="10"/>
-        <v>46515</v>
-      </c>
-      <c r="N52" s="63">
+        <v>46530</v>
+      </c>
+      <c r="N52" s="57">
         <v>22</v>
       </c>
-      <c r="O52" s="68">
+      <c r="O52" s="62">
         <f t="shared" si="11"/>
-        <v>46537</v>
+        <v>46552</v>
       </c>
       <c r="P52" s="42"/>
-      <c r="Q52" s="61" t="s">
+      <c r="Q52" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="R52" s="69">
+      <c r="R52" s="63">
         <f t="shared" si="12"/>
-        <v>46515</v>
-      </c>
-      <c r="S52" s="63">
+        <v>46530</v>
+      </c>
+      <c r="S52" s="57">
         <v>22</v>
       </c>
-      <c r="T52" s="68">
+      <c r="T52" s="62">
         <f t="shared" si="13"/>
-        <v>46537</v>
+        <v>46552</v>
       </c>
       <c r="U52" s="42"/>
-      <c r="V52" s="72" t="s">
+      <c r="V52" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="W52" s="69">
+      <c r="W52" s="63">
         <f t="shared" si="6"/>
-        <v>46542</v>
-      </c>
-      <c r="X52" s="63">
+        <v>46557</v>
+      </c>
+      <c r="X52" s="57">
         <v>45</v>
       </c>
-      <c r="Y52" s="68">
+      <c r="Y52" s="62">
         <f t="shared" si="14"/>
-        <v>46587</v>
+        <v>46602</v>
       </c>
       <c r="Z52" s="42"/>
-      <c r="AA52" s="61" t="s">
+      <c r="AA52" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="AB52" s="69">
+      <c r="AB52" s="63">
         <f t="shared" si="7"/>
-        <v>46534</v>
-      </c>
-      <c r="AC52" s="63">
+        <v>46557</v>
+      </c>
+      <c r="AC52" s="57">
         <v>45</v>
       </c>
-      <c r="AD52" s="87">
+      <c r="AD52" s="81">
         <f t="shared" si="15"/>
-        <v>46579</v>
+        <v>46602</v>
       </c>
     </row>
     <row r="53" spans="2:30" s="15" customFormat="1" ht="22" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B53" s="61" t="s">
+      <c r="B53" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="C53" s="62">
+      <c r="C53" s="56">
         <f t="shared" si="8"/>
         <v>46515</v>
       </c>
-      <c r="D53" s="63">
+      <c r="D53" s="57">
         <v>22</v>
       </c>
-      <c r="E53" s="87">
+      <c r="E53" s="81">
         <f t="shared" si="9"/>
         <v>46537</v>
       </c>
       <c r="F53" s="42"/>
-      <c r="G53" s="61" t="s">
+      <c r="G53" s="55" t="s">
         <v>59</v>
       </c>
-      <c r="H53" s="62">
+      <c r="H53" s="56">
         <f>J52</f>
         <v>46515</v>
       </c>
-      <c r="I53" s="63">
+      <c r="I53" s="57">
         <v>22</v>
       </c>
-      <c r="J53" s="87">
+      <c r="J53" s="81">
         <f>I53+H53</f>
         <v>46537</v>
       </c>
-      <c r="K53" s="88"/>
-      <c r="L53" s="73" t="s">
+      <c r="K53" s="82"/>
+      <c r="L53" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="M53" s="89">
+      <c r="M53" s="83">
         <f>O26</f>
-        <v>46198</v>
+        <v>46214</v>
       </c>
       <c r="N53" s="15">
         <v>425</v>
       </c>
-      <c r="O53" s="90">
+      <c r="O53" s="84">
         <f>N53+M53</f>
-        <v>46623</v>
-      </c>
-      <c r="Q53" s="73" t="s">
+        <v>46639</v>
+      </c>
+      <c r="Q53" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="R53" s="89">
+      <c r="R53" s="83">
         <f>T27</f>
-        <v>46215</v>
+        <v>46236</v>
       </c>
       <c r="S53" s="15">
         <v>453</v>
       </c>
-      <c r="T53" s="90">
+      <c r="T53" s="84">
         <f>S53+R53</f>
-        <v>46668</v>
-      </c>
-      <c r="V53" s="80" t="s">
+        <v>46689</v>
+      </c>
+      <c r="V53" s="74" t="s">
         <v>60</v>
       </c>
-      <c r="W53" s="89">
+      <c r="W53" s="83">
         <f>Y25</f>
-        <v>46221</v>
+        <v>46228</v>
       </c>
       <c r="X53" s="15">
         <v>439</v>
       </c>
-      <c r="Y53" s="90">
+      <c r="Y53" s="84">
         <f>X53+W53</f>
-        <v>46660</v>
-      </c>
-      <c r="AA53" s="73" t="s">
+        <v>46667</v>
+      </c>
+      <c r="AA53" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="AB53" s="89">
+      <c r="AB53" s="83">
         <f>AD24</f>
-        <v>46197</v>
+        <v>46209</v>
       </c>
       <c r="AC53" s="15">
         <v>425</v>
       </c>
-      <c r="AD53" s="90">
+      <c r="AD53" s="84">
         <f>AC53+AB53</f>
-        <v>46622</v>
+        <v>46634</v>
       </c>
     </row>
     <row r="54" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
-      <c r="B54" s="91" t="s">
+      <c r="B54" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="C54" s="92">
+      <c r="C54" s="86">
         <f>E29</f>
-        <v>46210</v>
+        <v>46219</v>
       </c>
       <c r="D54" s="15">
         <v>430</v>
       </c>
-      <c r="E54" s="90">
+      <c r="E54" s="84">
         <f>D54+C54</f>
-        <v>46640</v>
-      </c>
-      <c r="G54" s="91" t="s">
+        <v>46649</v>
+      </c>
+      <c r="G54" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="H54" s="92">
+      <c r="H54" s="86">
         <f>J28+11</f>
-        <v>46190</v>
+        <v>46203</v>
       </c>
       <c r="I54" s="15">
         <v>402</v>
       </c>
-      <c r="J54" s="90">
+      <c r="J54" s="84">
         <f>J53+30</f>
         <v>46567</v>
       </c>
-      <c r="L54" s="93"/>
+      <c r="L54" s="87"/>
       <c r="M54" s="16"/>
       <c r="N54" s="16"/>
-      <c r="O54" s="94"/>
-      <c r="Q54" s="93"/>
+      <c r="O54" s="88"/>
+      <c r="Q54" s="87"/>
       <c r="R54" s="16"/>
       <c r="S54" s="16"/>
-      <c r="T54" s="94"/>
-      <c r="V54" s="82"/>
+      <c r="T54" s="88"/>
+      <c r="V54" s="76"/>
       <c r="W54" s="16"/>
       <c r="X54" s="16"/>
-      <c r="Y54" s="94"/>
-      <c r="AA54" s="93"/>
+      <c r="Y54" s="88"/>
+      <c r="AA54" s="87"/>
       <c r="AB54" s="16"/>
       <c r="AC54" s="16"/>
-      <c r="AD54" s="94"/>
-    </row>
-    <row r="55" spans="2:30" s="99" customFormat="1" ht="64.5" x14ac:dyDescent="0.9">
-      <c r="B55" s="95" t="s">
+      <c r="AD54" s="88"/>
+    </row>
+    <row r="55" spans="2:30" s="93" customFormat="1" ht="64.5" x14ac:dyDescent="0.9">
+      <c r="B55" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="C55" s="96">
+      <c r="C55" s="90">
         <f>C54+8</f>
-        <v>46218</v>
-      </c>
-      <c r="D55" s="97">
+        <v>46227</v>
+      </c>
+      <c r="D55" s="91">
         <v>650</v>
       </c>
-      <c r="E55" s="94">
+      <c r="E55" s="88">
         <f>D55+C55</f>
-        <v>46868</v>
-      </c>
-      <c r="F55" s="98"/>
-      <c r="G55" s="95" t="s">
+        <v>46877</v>
+      </c>
+      <c r="F55" s="92"/>
+      <c r="G55" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="H55" s="96">
+      <c r="H55" s="90">
         <f t="shared" ref="H55:J56" si="22">C55</f>
-        <v>46218</v>
-      </c>
-      <c r="I55" s="97">
+        <v>46227</v>
+      </c>
+      <c r="I55" s="91">
         <f t="shared" si="22"/>
         <v>650</v>
       </c>
-      <c r="J55" s="94">
+      <c r="J55" s="88">
         <f t="shared" si="22"/>
-        <v>46868</v>
+        <v>46877</v>
       </c>
       <c r="K55" s="15"/>
-      <c r="L55" s="95" t="s">
+      <c r="L55" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="M55" s="96">
+      <c r="M55" s="90">
         <f t="shared" ref="M55:O56" si="23">H55</f>
-        <v>46218</v>
-      </c>
-      <c r="N55" s="97">
+        <v>46227</v>
+      </c>
+      <c r="N55" s="91">
         <f t="shared" si="23"/>
         <v>650</v>
       </c>
-      <c r="O55" s="94">
+      <c r="O55" s="88">
         <f t="shared" si="23"/>
-        <v>46868</v>
-      </c>
-      <c r="P55" s="98"/>
-      <c r="Q55" s="95" t="s">
+        <v>46877</v>
+      </c>
+      <c r="P55" s="92"/>
+      <c r="Q55" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="R55" s="96">
+      <c r="R55" s="90">
         <f t="shared" ref="R55:T56" si="24">M55</f>
-        <v>46218</v>
-      </c>
-      <c r="S55" s="97">
+        <v>46227</v>
+      </c>
+      <c r="S55" s="91">
         <f t="shared" si="24"/>
         <v>650</v>
       </c>
-      <c r="T55" s="94">
+      <c r="T55" s="88">
         <f t="shared" si="24"/>
-        <v>46868</v>
+        <v>46877</v>
       </c>
       <c r="U55" s="15"/>
-      <c r="V55" s="95" t="s">
+      <c r="V55" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="W55" s="96">
+      <c r="W55" s="90">
         <f t="shared" ref="W55:Y56" si="25">R55</f>
-        <v>46218</v>
-      </c>
-      <c r="X55" s="97">
+        <v>46227</v>
+      </c>
+      <c r="X55" s="91">
         <f t="shared" si="25"/>
         <v>650</v>
       </c>
-      <c r="Y55" s="94">
+      <c r="Y55" s="88">
         <f t="shared" si="25"/>
-        <v>46868</v>
-      </c>
-      <c r="Z55" s="98"/>
-      <c r="AA55" s="95" t="s">
+        <v>46877</v>
+      </c>
+      <c r="Z55" s="92"/>
+      <c r="AA55" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="AB55" s="96">
+      <c r="AB55" s="90">
         <f t="shared" ref="AB55:AD56" si="26">W55</f>
-        <v>46218</v>
-      </c>
-      <c r="AC55" s="97">
+        <v>46227</v>
+      </c>
+      <c r="AC55" s="91">
         <f t="shared" si="26"/>
         <v>650</v>
       </c>
-      <c r="AD55" s="94">
+      <c r="AD55" s="88">
         <f t="shared" si="26"/>
-        <v>46868</v>
+        <v>46877</v>
       </c>
     </row>
     <row r="56" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
-      <c r="B56" s="93" t="s">
+      <c r="B56" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="C56" s="96">
+      <c r="C56" s="90">
         <f>C55+45</f>
-        <v>46263</v>
-      </c>
-      <c r="D56" s="100">
-        <v>640</v>
-      </c>
-      <c r="E56" s="94">
+        <v>46272</v>
+      </c>
+      <c r="D56" s="94">
+        <v>631</v>
+      </c>
+      <c r="E56" s="88">
         <f>D56+C56</f>
         <v>46903</v>
       </c>
-      <c r="F56" s="97"/>
-      <c r="G56" s="93" t="s">
+      <c r="F56" s="91"/>
+      <c r="G56" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="H56" s="96">
+      <c r="H56" s="90">
         <f t="shared" si="22"/>
-        <v>46263</v>
-      </c>
-      <c r="I56" s="100">
+        <v>46272</v>
+      </c>
+      <c r="I56" s="94">
         <f t="shared" si="22"/>
-        <v>640</v>
-      </c>
-      <c r="J56" s="94">
+        <v>631</v>
+      </c>
+      <c r="J56" s="88">
         <f t="shared" si="22"/>
         <v>46903</v>
       </c>
-      <c r="K56" s="101"/>
-      <c r="L56" s="93" t="s">
+      <c r="K56" s="95"/>
+      <c r="L56" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="M56" s="96">
+      <c r="M56" s="90">
         <f t="shared" si="23"/>
-        <v>46263</v>
-      </c>
-      <c r="N56" s="100">
+        <v>46272</v>
+      </c>
+      <c r="N56" s="94">
         <f t="shared" si="23"/>
-        <v>640</v>
-      </c>
-      <c r="O56" s="94">
+        <v>631</v>
+      </c>
+      <c r="O56" s="88">
         <f t="shared" si="23"/>
         <v>46903</v>
       </c>
-      <c r="P56" s="101"/>
-      <c r="Q56" s="93" t="s">
+      <c r="P56" s="95"/>
+      <c r="Q56" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="R56" s="96">
+      <c r="R56" s="90">
         <f t="shared" si="24"/>
-        <v>46263</v>
-      </c>
-      <c r="S56" s="100">
+        <v>46272</v>
+      </c>
+      <c r="S56" s="94">
         <f t="shared" si="24"/>
-        <v>640</v>
-      </c>
-      <c r="T56" s="94">
+        <v>631</v>
+      </c>
+      <c r="T56" s="88">
         <f t="shared" si="24"/>
         <v>46903</v>
       </c>
-      <c r="U56" s="101"/>
-      <c r="V56" s="93" t="s">
+      <c r="U56" s="95"/>
+      <c r="V56" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="W56" s="96">
+      <c r="W56" s="90">
         <f t="shared" si="25"/>
-        <v>46263</v>
-      </c>
-      <c r="X56" s="100">
+        <v>46272</v>
+      </c>
+      <c r="X56" s="94">
         <f t="shared" si="25"/>
-        <v>640</v>
-      </c>
-      <c r="Y56" s="94">
+        <v>631</v>
+      </c>
+      <c r="Y56" s="88">
         <f t="shared" si="25"/>
         <v>46903</v>
       </c>
-      <c r="Z56" s="101"/>
-      <c r="AA56" s="93" t="s">
+      <c r="Z56" s="95"/>
+      <c r="AA56" s="87" t="s">
         <v>63</v>
       </c>
-      <c r="AB56" s="96">
+      <c r="AB56" s="90">
         <f t="shared" si="26"/>
-        <v>46263</v>
-      </c>
-      <c r="AC56" s="100">
+        <v>46272</v>
+      </c>
+      <c r="AC56" s="94">
         <f t="shared" si="26"/>
-        <v>640</v>
-      </c>
-      <c r="AD56" s="94">
+        <v>631</v>
+      </c>
+      <c r="AD56" s="88">
         <f t="shared" si="26"/>
         <v>46903</v>
       </c>
     </row>
     <row r="57" spans="2:30" s="15" customFormat="1" x14ac:dyDescent="0.9">
-      <c r="B57" s="102" t="s">
+      <c r="B57" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="C57" s="103">
+      <c r="C57" s="97">
         <f>E56</f>
         <v>46903</v>
       </c>
-      <c r="D57" s="104"/>
-      <c r="E57" s="105">
+      <c r="D57" s="98"/>
+      <c r="E57" s="99">
         <f>C57</f>
         <v>46903</v>
       </c>
-      <c r="F57" s="101"/>
-      <c r="G57" s="102" t="s">
+      <c r="F57" s="95"/>
+      <c r="G57" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="H57" s="103">
+      <c r="H57" s="97">
         <f>C57</f>
         <v>46903</v>
       </c>
-      <c r="I57" s="104"/>
-      <c r="J57" s="105">
+      <c r="I57" s="98"/>
+      <c r="J57" s="99">
         <f>E57</f>
         <v>46903</v>
       </c>
-      <c r="K57" s="101"/>
-      <c r="L57" s="102" t="s">
+      <c r="K57" s="95"/>
+      <c r="L57" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="M57" s="103">
+      <c r="M57" s="97">
         <f>H57</f>
         <v>46903</v>
       </c>
-      <c r="N57" s="104"/>
-      <c r="O57" s="105">
+      <c r="N57" s="98"/>
+      <c r="O57" s="99">
         <f>J57</f>
         <v>46903</v>
       </c>
-      <c r="P57" s="101"/>
-      <c r="Q57" s="102" t="s">
+      <c r="P57" s="95"/>
+      <c r="Q57" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="R57" s="103">
+      <c r="R57" s="97">
         <f>M57</f>
         <v>46903</v>
       </c>
-      <c r="S57" s="104"/>
-      <c r="T57" s="105">
+      <c r="S57" s="98"/>
+      <c r="T57" s="99">
         <f>O57</f>
         <v>46903</v>
       </c>
-      <c r="U57" s="101"/>
-      <c r="V57" s="102" t="s">
+      <c r="U57" s="95"/>
+      <c r="V57" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="W57" s="103">
+      <c r="W57" s="97">
         <f>R57</f>
         <v>46903</v>
       </c>
-      <c r="X57" s="104"/>
-      <c r="Y57" s="105">
+      <c r="X57" s="98"/>
+      <c r="Y57" s="99">
         <f>T57</f>
         <v>46903</v>
       </c>
-      <c r="Z57" s="101"/>
-      <c r="AA57" s="102" t="s">
+      <c r="Z57" s="95"/>
+      <c r="AA57" s="96" t="s">
         <v>64</v>
       </c>
-      <c r="AB57" s="103">
+      <c r="AB57" s="97">
         <f>W57</f>
         <v>46903</v>
       </c>
-      <c r="AC57" s="104"/>
-      <c r="AD57" s="105">
+      <c r="AC57" s="98"/>
+      <c r="AD57" s="99">
         <f>Y57</f>
         <v>46903</v>
       </c>
     </row>
     <row r="58" spans="2:30" s="15" customFormat="1" ht="43.5" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B58" s="106" t="s">
+      <c r="B58" s="100" t="s">
         <v>80</v>
       </c>
-      <c r="C58" s="103">
+      <c r="C58" s="101">
         <v>46993</v>
       </c>
-      <c r="D58" s="108"/>
-      <c r="E58" s="109"/>
-      <c r="F58" s="101"/>
-      <c r="G58" s="106" t="str">
+      <c r="D58" s="102"/>
+      <c r="E58" s="103"/>
+      <c r="F58" s="95"/>
+      <c r="G58" s="100" t="str">
         <f>B58</f>
         <v xml:space="preserve">Start of Handover </v>
       </c>
-      <c r="H58" s="107">
+      <c r="H58" s="101">
         <f>C58</f>
         <v>46993</v>
       </c>
-      <c r="I58" s="108"/>
-      <c r="J58" s="109"/>
-      <c r="K58" s="101"/>
-      <c r="L58" s="110" t="str">
+      <c r="I58" s="102"/>
+      <c r="J58" s="103"/>
+      <c r="K58" s="95"/>
+      <c r="L58" s="104" t="str">
         <f>G58</f>
         <v xml:space="preserve">Start of Handover </v>
       </c>
-      <c r="M58" s="107">
+      <c r="M58" s="101">
         <f>H58</f>
         <v>46993</v>
       </c>
-      <c r="N58" s="108"/>
-      <c r="O58" s="109"/>
-      <c r="P58" s="101"/>
-      <c r="Q58" s="110" t="str">
+      <c r="N58" s="102"/>
+      <c r="O58" s="103"/>
+      <c r="P58" s="95"/>
+      <c r="Q58" s="104" t="str">
         <f>L58</f>
         <v xml:space="preserve">Start of Handover </v>
       </c>
-      <c r="R58" s="107">
+      <c r="R58" s="101">
         <f>M58</f>
         <v>46993</v>
       </c>
-      <c r="S58" s="108"/>
-      <c r="T58" s="109"/>
-      <c r="U58" s="101"/>
-      <c r="V58" s="110" t="str">
+      <c r="S58" s="102"/>
+      <c r="T58" s="103"/>
+      <c r="U58" s="95"/>
+      <c r="V58" s="104" t="str">
         <f>Q58</f>
         <v xml:space="preserve">Start of Handover </v>
       </c>
-      <c r="W58" s="107">
+      <c r="W58" s="101">
         <f>R58</f>
         <v>46993</v>
       </c>
-      <c r="X58" s="108"/>
-      <c r="Y58" s="109"/>
-      <c r="Z58" s="101"/>
-      <c r="AA58" s="110" t="str">
+      <c r="X58" s="102"/>
+      <c r="Y58" s="103"/>
+      <c r="Z58" s="95"/>
+      <c r="AA58" s="104" t="str">
         <f>V58</f>
         <v xml:space="preserve">Start of Handover </v>
       </c>
-      <c r="AB58" s="107">
+      <c r="AB58" s="101">
         <f>W58</f>
         <v>46993</v>
       </c>
-      <c r="AC58" s="108"/>
-      <c r="AD58" s="109"/>
+      <c r="AC58" s="102"/>
+      <c r="AD58" s="103"/>
     </row>
     <row r="59" spans="2:30" x14ac:dyDescent="0.9">
-      <c r="M59" s="103"/>
+      <c r="M59" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7702,10 +7705,10 @@
   <dimension ref="B2:H22"/>
   <sheetFormatPr defaultColWidth="41" defaultRowHeight="21.5" x14ac:dyDescent="0.9"/>
   <cols>
-    <col min="1" max="1" width="8.6328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="53.08984375" style="2" customWidth="1"/>
-    <col min="3" max="8" width="16.36328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="4.6328125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="8.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="53.1796875" style="2" customWidth="1"/>
+    <col min="3" max="8" width="16.453125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="4.54296875" style="2" customWidth="1"/>
     <col min="10" max="16384" width="41" style="2"/>
   </cols>
   <sheetData>
@@ -7733,33 +7736,33 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+    <row r="4" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B4" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="148" t="s">
+      <c r="C4" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="149"/>
-      <c r="E4" s="149"/>
-      <c r="F4" s="149"/>
-      <c r="G4" s="149"/>
-      <c r="H4" s="150"/>
-    </row>
-    <row r="5" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="D4" s="132"/>
+      <c r="E4" s="132"/>
+      <c r="F4" s="132"/>
+      <c r="G4" s="132"/>
+      <c r="H4" s="133"/>
+    </row>
+    <row r="5" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B5" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="148" t="s">
+      <c r="C5" s="131" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="149"/>
-      <c r="E5" s="149"/>
-      <c r="F5" s="149"/>
-      <c r="G5" s="149"/>
-      <c r="H5" s="150"/>
-    </row>
-    <row r="6" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="D5" s="132"/>
+      <c r="E5" s="132"/>
+      <c r="F5" s="132"/>
+      <c r="G5" s="132"/>
+      <c r="H5" s="133"/>
+    </row>
+    <row r="6" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
       <c r="B6" s="5" t="s">
         <v>70</v>
       </c>
@@ -7782,11 +7785,11 @@
         <v>45292</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="B7" s="151" t="s">
+    <row r="7" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B7" s="134" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="153">
+      <c r="C7" s="136">
         <v>45839</v>
       </c>
       <c r="D7" s="6">
@@ -7798,16 +7801,16 @@
       <c r="F7" s="6">
         <v>45839</v>
       </c>
-      <c r="G7" s="155">
+      <c r="G7" s="138">
         <v>45778</v>
       </c>
       <c r="H7" s="6">
         <v>45778</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B8" s="152"/>
-      <c r="C8" s="154"/>
+    <row r="8" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B8" s="135"/>
+      <c r="C8" s="137"/>
       <c r="D8" s="7">
         <v>45870</v>
       </c>
@@ -7817,16 +7820,16 @@
       <c r="F8" s="7">
         <v>45901</v>
       </c>
-      <c r="G8" s="156"/>
+      <c r="G8" s="139"/>
       <c r="H8" s="7">
         <v>45839</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B9" s="151" t="s">
+    <row r="9" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B9" s="134" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="112">
+      <c r="C9" s="106">
         <v>45962</v>
       </c>
       <c r="D9" s="9">
@@ -7845,32 +7848,32 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B10" s="152"/>
-      <c r="C10" s="113">
+    <row r="10" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B10" s="135"/>
+      <c r="C10" s="107">
         <v>46023</v>
       </c>
-      <c r="D10" s="113">
+      <c r="D10" s="107">
         <v>46054</v>
       </c>
-      <c r="E10" s="113">
+      <c r="E10" s="107">
         <v>46082</v>
       </c>
-      <c r="F10" s="113">
+      <c r="F10" s="107">
         <v>46082</v>
       </c>
-      <c r="G10" s="113">
+      <c r="G10" s="107">
         <v>46357</v>
       </c>
-      <c r="H10" s="113">
+      <c r="H10" s="107">
         <v>46023</v>
       </c>
     </row>
-    <row r="11" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B11" s="151" t="s">
+    <row r="11" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B11" s="134" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="114">
+      <c r="C11" s="108">
         <v>46113</v>
       </c>
       <c r="D11" s="9">
@@ -7889,38 +7892,38 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="12" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B12" s="152"/>
-      <c r="C12" s="115">
-        <f>'01.06.26 Revised'!O26</f>
-        <v>46198</v>
+    <row r="12" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B12" s="135"/>
+      <c r="C12" s="109">
+        <f>'29.06.26 Revised'!O26</f>
+        <v>46214</v>
       </c>
       <c r="D12" s="10">
-        <f>'01.06.26 Revised'!T26</f>
-        <v>46203</v>
+        <f>'29.06.26 Revised'!T26</f>
+        <v>46225</v>
       </c>
       <c r="E12" s="10">
-        <f>'01.06.26 Revised'!Y26</f>
-        <v>46233</v>
+        <f>'29.06.26 Revised'!Y26</f>
+        <v>46239</v>
       </c>
       <c r="F12" s="10">
-        <f>'01.06.26 Revised'!AD26</f>
-        <v>46221</v>
-      </c>
-      <c r="G12" s="113">
-        <f>'01.06.26 Revised'!J26</f>
+        <f>'29.06.26 Revised'!AD26</f>
+        <v>46232</v>
+      </c>
+      <c r="G12" s="107">
+        <f>'29.06.26 Revised'!J26</f>
         <v>46149</v>
       </c>
-      <c r="H12" s="113">
-        <f>'01.06.26 Revised'!E26</f>
+      <c r="H12" s="107">
+        <f>'29.06.26 Revised'!E26</f>
         <v>46170</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="B13" s="151" t="s">
+    <row r="13" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B13" s="134" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="114">
+      <c r="C13" s="108">
         <v>46235</v>
       </c>
       <c r="D13" s="9">
@@ -7939,15 +7942,15 @@
         <v>46204</v>
       </c>
     </row>
-    <row r="14" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B14" s="152"/>
-      <c r="C14" s="115">
-        <f>'01.06.26 Revised'!O36</f>
-        <v>46320</v>
+    <row r="14" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B14" s="135"/>
+      <c r="C14" s="109">
+        <f>'29.06.26 Revised'!O36</f>
+        <v>46335</v>
       </c>
       <c r="D14" s="10">
-        <f>'01.06.26 Revised'!T36</f>
-        <v>46323</v>
+        <f>'29.06.26 Revised'!T36</f>
+        <v>46339</v>
       </c>
       <c r="E14" s="10">
         <v>46357</v>
@@ -7963,49 +7966,49 @@
         <v>46327</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="B15" s="151" t="s">
+    <row r="15" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B15" s="134" t="s">
         <v>81</v>
       </c>
-      <c r="C15" s="114"/>
+      <c r="C15" s="108"/>
       <c r="D15" s="9"/>
       <c r="E15" s="9"/>
       <c r="F15" s="9"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
     </row>
-    <row r="16" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B16" s="152"/>
+    <row r="16" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B16" s="135"/>
       <c r="C16" s="12">
-        <f>'01.06.26 Revised'!O49</f>
+        <f>'29.06.26 Revised'!O49</f>
+        <v>46492</v>
+      </c>
+      <c r="D16" s="11">
+        <f>'29.06.26 Revised'!T49</f>
+        <v>46492</v>
+      </c>
+      <c r="E16" s="11">
+        <f>'29.06.26 Revised'!Y49</f>
+        <v>46507</v>
+      </c>
+      <c r="F16" s="11">
+        <f>'29.06.26 Revised'!AD49</f>
+        <v>46507</v>
+      </c>
+      <c r="G16" s="11">
+        <f>'29.06.26 Revised'!E50</f>
         <v>46477</v>
       </c>
-      <c r="D16" s="11">
-        <f>'01.06.26 Revised'!T49</f>
+      <c r="H16" s="11">
+        <f>'29.06.26 Revised'!J50</f>
         <v>46477</v>
       </c>
-      <c r="E16" s="11">
-        <f>'01.06.26 Revised'!Y49</f>
-        <v>46492</v>
-      </c>
-      <c r="F16" s="11">
-        <f>'01.06.26 Revised'!AD49</f>
-        <v>46484</v>
-      </c>
-      <c r="G16" s="11">
-        <f>'01.06.26 Revised'!E50</f>
-        <v>46477</v>
-      </c>
-      <c r="H16" s="11">
-        <f>'01.06.26 Revised'!J50</f>
-        <v>46477</v>
-      </c>
-    </row>
-    <row r="17" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="B17" s="151" t="s">
+    </row>
+    <row r="17" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B17" s="134" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="114">
+      <c r="C17" s="108">
         <v>46447</v>
       </c>
       <c r="D17" s="9">
@@ -8024,84 +8027,84 @@
         <v>46419</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B18" s="152"/>
+    <row r="18" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B18" s="135"/>
       <c r="C18" s="12">
-        <f>'01.06.26 Revised'!O52</f>
+        <f>'29.06.26 Revised'!O52</f>
+        <v>46552</v>
+      </c>
+      <c r="D18" s="11">
+        <f>'29.06.26 Revised'!T52</f>
+        <v>46552</v>
+      </c>
+      <c r="E18" s="11">
+        <f>'29.06.26 Revised'!Y52</f>
+        <v>46602</v>
+      </c>
+      <c r="F18" s="11">
+        <f>'29.06.26 Revised'!AD52</f>
+        <v>46602</v>
+      </c>
+      <c r="G18" s="11">
+        <f>'29.06.26 Revised'!E53</f>
         <v>46537</v>
       </c>
-      <c r="D18" s="11">
-        <f>'01.06.26 Revised'!T52</f>
+      <c r="H18" s="11">
+        <f>'29.06.26 Revised'!J53</f>
         <v>46537</v>
       </c>
-      <c r="E18" s="11">
-        <f>'01.06.26 Revised'!Y52</f>
-        <v>46587</v>
-      </c>
-      <c r="F18" s="11">
-        <f>'01.06.26 Revised'!AD52</f>
-        <v>46579</v>
-      </c>
-      <c r="G18" s="11">
-        <f>'01.06.26 Revised'!E53</f>
-        <v>46537</v>
-      </c>
-      <c r="H18" s="11">
-        <f>'01.06.26 Revised'!J53</f>
-        <v>46537</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" ht="20" customHeight="1" x14ac:dyDescent="0.9">
-      <c r="B19" s="151" t="s">
+    </row>
+    <row r="19" spans="2:8" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.9">
+      <c r="B19" s="134" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="161">
+      <c r="C19" s="144">
         <v>46722</v>
       </c>
-      <c r="D19" s="161"/>
-      <c r="E19" s="161"/>
-      <c r="F19" s="161"/>
-      <c r="G19" s="161"/>
-      <c r="H19" s="162"/>
-    </row>
-    <row r="20" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B20" s="152"/>
-      <c r="C20" s="163">
-        <f>'01.06.26 Revised'!E57</f>
+      <c r="D19" s="144"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="144"/>
+      <c r="G19" s="144"/>
+      <c r="H19" s="145"/>
+    </row>
+    <row r="20" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B20" s="135"/>
+      <c r="C20" s="146">
+        <f>'29.06.26 Revised'!E57</f>
         <v>46903</v>
       </c>
-      <c r="D20" s="163"/>
-      <c r="E20" s="163"/>
-      <c r="F20" s="163"/>
-      <c r="G20" s="163"/>
-      <c r="H20" s="164"/>
-    </row>
-    <row r="21" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B21" s="111" t="s">
+      <c r="D20" s="146"/>
+      <c r="E20" s="146"/>
+      <c r="F20" s="146"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="147"/>
+    </row>
+    <row r="21" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B21" s="105" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="157">
-        <f>'01.06.26 Revised'!E58</f>
+      <c r="C21" s="140">
+        <f>'29.06.26 Revised'!E58</f>
         <v>0</v>
       </c>
-      <c r="D21" s="157"/>
-      <c r="E21" s="157"/>
-      <c r="F21" s="157"/>
-      <c r="G21" s="157"/>
-      <c r="H21" s="158"/>
-    </row>
-    <row r="22" spans="2:8" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
-      <c r="B22" s="111" t="s">
+      <c r="D21" s="140"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
+      <c r="G21" s="140"/>
+      <c r="H21" s="141"/>
+    </row>
+    <row r="22" spans="2:8" ht="20.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.95">
+      <c r="B22" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="159" t="s">
+      <c r="C22" s="142" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="159"/>
-      <c r="E22" s="159"/>
-      <c r="F22" s="159"/>
-      <c r="G22" s="159"/>
-      <c r="H22" s="160"/>
+      <c r="D22" s="142"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="142"/>
+      <c r="G22" s="142"/>
+      <c r="H22" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="15">
